--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Späd brosklav
 Blodticka
 Bårdlav
+Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -781,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1403,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1744,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1852,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1957,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1973,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1997,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2009,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2400,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2495,7 +2496,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53264-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2505,14 +2506,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2525,23 +2526,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>100.3</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2549,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2561,367 +2562,367 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" t="n">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
@@ -2945,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3048,14 +3049,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3068,10 +3069,10 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -3080,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3092,10 +3093,10 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3104,46 +3105,50 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3157,10 +3162,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46037</v>
+        <v>45258</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3173,16 +3178,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>19.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3197,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3206,49 +3211,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3262,10 +3271,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45326</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3278,7 +3287,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3314,46 +3323,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3367,10 +3376,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45405</v>
+        <v>45326</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3383,7 +3392,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3423,42 +3432,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3472,10 +3481,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46265</v>
+        <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3488,7 +3497,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3524,46 +3533,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3577,10 +3586,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45645</v>
+        <v>46265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3593,17 +3602,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3617,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3629,50 +3638,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3682,14 +3687,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45258</v>
+        <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3702,20 +3707,20 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19.8</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -3726,55 +3731,51 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
@@ -3798,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3876,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3955,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4083,7 +4084,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4097,10 +4098,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45361</v>
+        <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4113,7 +4114,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4156,7 +4157,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4170,10 +4171,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45331</v>
+        <v>45596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4186,7 +4187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>17.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4229,7 +4230,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4243,10 +4244,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45447</v>
+        <v>45217</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4259,7 +4260,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>1.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4302,7 +4303,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4316,10 +4317,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44979</v>
+        <v>45447</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4331,13 +4332,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4380,7 +4376,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4397,7 +4393,7 @@
         <v>44916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4410,7 +4406,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4453,7 +4449,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4467,10 +4463,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45447</v>
+        <v>46024</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4483,7 +4479,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>15.6</v>
+        <v>10.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4526,7 +4522,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4536,14 +4532,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45333</v>
+        <v>44805</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4556,7 +4552,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4599,7 +4595,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4613,10 +4609,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45426</v>
+        <v>46037</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4629,7 +4625,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>62.1</v>
+        <v>31.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4672,7 +4668,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4689,7 +4685,7 @@
         <v>45848</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4702,7 +4698,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4745,7 +4741,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4762,7 +4758,7 @@
         <v>45848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4775,7 +4771,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4818,7 +4814,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4832,10 +4828,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44979</v>
+        <v>45944</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4853,7 +4849,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>22.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4896,7 +4892,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4910,10 +4906,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44721</v>
+        <v>46094</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4926,7 +4922,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>11.8</v>
+        <v>24.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4969,7 +4965,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4979,14 +4975,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44916</v>
+        <v>46108</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4998,8 +4994,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5042,7 +5043,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5056,10 +5057,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44916</v>
+        <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,7 +5073,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>13.4</v>
+        <v>27.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5115,7 +5116,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5129,10 +5130,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45588</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5144,13 +5145,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>20.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5193,7 +5189,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5207,10 +5203,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45944</v>
+        <v>46126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5222,13 +5218,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>22.6</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5271,7 +5262,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5281,14 +5272,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44805</v>
+        <v>46092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5301,7 +5292,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.1</v>
+        <v>37.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5344,7 +5335,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5358,10 +5349,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,7 +5365,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>24.5</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5417,7 +5408,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 12984-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5431,10 +5422,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45777</v>
+        <v>46092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5438,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>20.1</v>
+        <v>18.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5490,7 +5481,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5500,14 +5491,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45776</v>
+        <v>45334</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5511,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>27.3</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5563,7 +5554,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5573,14 +5564,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46108</v>
+        <v>45361</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5592,13 +5583,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.7</v>
+        <v>8.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5641,7 +5627,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5655,10 +5641,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46126</v>
+        <v>45331</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5671,7 +5657,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5714,7 +5700,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5728,10 +5714,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46092</v>
+        <v>44748</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5744,7 +5730,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>37.2</v>
+        <v>15.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5787,7 +5773,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5801,10 +5787,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46092</v>
+        <v>44979</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5816,8 +5802,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>18.2</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5860,7 +5851,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5870,14 +5861,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46092</v>
+        <v>45293</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5890,7 +5881,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5933,7 +5924,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5947,10 +5938,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45596</v>
+        <v>45162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5963,7 +5954,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.4</v>
+        <v>51.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6006,7 +5997,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6016,14 +6007,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>45236</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6035,8 +6026,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6079,7 +6075,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6093,10 +6089,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46024</v>
+        <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6109,7 +6105,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6152,7 +6148,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6166,10 +6162,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46037</v>
+        <v>46202</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6182,7 +6178,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>31.3</v>
+        <v>10.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6225,7 +6221,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6239,10 +6235,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45546</v>
+        <v>46202</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6255,7 +6251,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>39.8</v>
+        <v>2.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6298,7 +6294,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6312,10 +6308,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45387</v>
+        <v>46199</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6328,7 +6324,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.199999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6371,7 +6367,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6385,10 +6381,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45162</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6401,7 +6397,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>11.7</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6444,7 +6440,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6458,10 +6454,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45436</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6474,7 +6470,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.699999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6517,7 +6513,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6527,14 +6523,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44687</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6547,7 +6543,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6590,7 +6586,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6604,10 +6600,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44748</v>
+        <v>46265</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6620,7 +6616,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15.2</v>
+        <v>2.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6663,7 +6659,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6673,14 +6669,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45162</v>
+        <v>45588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6692,8 +6688,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6736,7 +6737,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 28533-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6750,10 +6751,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45162</v>
+        <v>46197</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6766,7 +6767,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>51.9</v>
+        <v>54.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6809,7 +6810,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6819,14 +6820,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45293</v>
+        <v>46147</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6839,7 +6840,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>35.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6882,7 +6883,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6896,10 +6897,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46202</v>
+        <v>44979</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6911,8 +6912,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6955,7 +6961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6969,10 +6975,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45042</v>
+        <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6984,13 +6990,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>10.7</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7033,7 +7034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7047,10 +7048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46199</v>
+        <v>45436</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7063,7 +7064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>16.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7106,7 +7107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7116,14 +7117,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46202</v>
+        <v>45042</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7133,6 +7134,11 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -7179,7 +7185,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7189,14 +7195,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46210</v>
+        <v>45708</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7208,8 +7214,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7252,7 +7263,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7266,10 +7277,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46210</v>
+        <v>45447</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7282,7 +7293,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>15.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7325,7 +7336,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7339,10 +7350,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46210</v>
+        <v>44916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,7 +7366,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7398,7 +7409,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 28533-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7412,10 +7423,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46197</v>
+        <v>45546</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,7 +7439,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>54.2</v>
+        <v>39.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7471,7 +7482,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7485,10 +7496,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44795</v>
+        <v>44721</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7501,7 +7512,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7544,7 +7555,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7554,14 +7565,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46265</v>
+        <v>44687</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7574,7 +7585,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7617,7 +7628,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7631,10 +7642,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46147</v>
+        <v>45333</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7647,7 +7658,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>35.7</v>
+        <v>1.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7690,7 +7701,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7700,14 +7711,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45334</v>
+        <v>44795</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7720,7 +7731,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.4</v>
+        <v>12.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7763,7 +7774,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7777,10 +7788,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45236</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7794,11 +7805,11 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7841,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7851,14 +7862,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45708</v>
+        <v>45426</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7870,13 +7881,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>0.8</v>
+        <v>62.1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7919,7 +7925,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7929,14 +7935,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45173</v>
+        <v>45387</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7948,13 +7954,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7997,7 +7998,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8011,10 +8012,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45217</v>
+        <v>44916</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8027,7 +8028,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8087,7 +8088,7 @@
         <v>45714</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 17740-2023</t>
+          <t>A 53264-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45035</v>
+        <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2635,22 +2635,17 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>20.1</v>
+        <v>100.3</v>
       </c>
       <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2665,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2677,252 +2672,257 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,17 +3069,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3105,50 +3105,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3158,14 +3154,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45258</v>
+        <v>44958</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,20 +3174,20 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>19.8</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -3202,62 +3198,58 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3271,10 +3263,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>45326</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3287,7 +3279,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>7.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3323,46 +3315,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3376,10 +3368,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45326</v>
+        <v>45405</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3392,7 +3384,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3432,42 +3424,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3481,10 +3473,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3497,7 +3489,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3533,46 +3525,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3586,10 +3578,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46265</v>
+        <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,16 +3594,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3626,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3638,46 +3630,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3687,14 +3683,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44958</v>
+        <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,10 +3703,10 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>19.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -3719,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3731,51 +3727,55 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>45361</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4028,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45162</v>
+        <v>45331</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.7</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45596</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>17.4</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4240,14 +4240,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45217</v>
+        <v>45162</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4303,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45447</v>
+        <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>51.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4386,14 +4386,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44916</v>
+        <v>45293</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>13.4</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46024</v>
+        <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44805</v>
+        <v>44979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4551,8 +4551,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4595,7 +4600,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46037</v>
+        <v>46094</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4625,7 +4630,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31.3</v>
+        <v>24.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4668,7 +4673,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4682,10 +4687,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45848</v>
+        <v>44916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4698,7 +4703,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4741,7 +4746,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4755,10 +4760,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45848</v>
+        <v>45447</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4771,7 +4776,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.4</v>
+        <v>15.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4814,7 +4819,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4824,14 +4829,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45944</v>
+        <v>46108</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4845,11 +4850,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>22.6</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4892,7 +4897,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4906,10 +4911,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46094</v>
+        <v>45333</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4922,7 +4927,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>24.5</v>
+        <v>1.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4965,7 +4970,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4975,14 +4980,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46108</v>
+        <v>46126</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4994,13 +4999,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45776</v>
+        <v>46092</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>27.3</v>
+        <v>37.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5116,7 +5116,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 12984-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>46092</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20.1</v>
+        <v>18.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5189,7 +5189,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46092</v>
+        <v>45944</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5291,8 +5291,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>37.2</v>
+        <v>22.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5335,7 +5340,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5349,10 +5354,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46092</v>
+        <v>45426</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5365,7 +5370,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>62.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5408,7 +5413,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46092</v>
+        <v>45777</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5438,7 +5443,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18.2</v>
+        <v>20.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5481,7 +5486,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5491,14 +5496,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45334</v>
+        <v>45776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5511,7 +5516,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.4</v>
+        <v>27.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5554,7 +5559,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45361</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5583,8 +5588,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5627,7 +5637,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5641,10 +5651,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45331</v>
+        <v>44721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5657,7 +5667,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.9</v>
+        <v>11.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5700,7 +5710,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5714,10 +5724,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44748</v>
+        <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5730,7 +5740,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>15.2</v>
+        <v>7.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5773,7 +5783,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5787,10 +5797,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44979</v>
+        <v>44916</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5802,13 +5812,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>4.6</v>
+        <v>13.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5851,7 +5856,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5861,14 +5866,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45293</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5880,8 +5885,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5924,7 +5934,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5934,14 +5944,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45162</v>
+        <v>44805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5954,7 +5964,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>51.9</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5997,7 +6007,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6007,14 +6017,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45236</v>
+        <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6026,13 +6036,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>6.6</v>
+        <v>17.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6075,7 +6080,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6092,7 +6097,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6105,7 +6110,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6148,7 +6153,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6162,10 +6167,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46202</v>
+        <v>46024</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6178,7 +6183,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6221,7 +6226,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6235,10 +6240,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46202</v>
+        <v>46037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6251,7 +6256,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.3</v>
+        <v>31.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6294,7 +6299,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,14 +6309,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46199</v>
+        <v>45042</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6323,8 +6328,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>16.9</v>
+        <v>10.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6367,7 +6377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6381,10 +6391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>45546</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6397,7 +6407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>39.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6440,7 +6450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6454,10 +6464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>45387</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6470,7 +6480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6513,7 +6523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6527,10 +6537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46210</v>
+        <v>44795</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6543,7 +6553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.8</v>
+        <v>12.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6586,7 +6596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6600,10 +6610,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46265</v>
+        <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6616,7 +6626,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.7</v>
+        <v>11.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6659,7 +6669,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6673,10 +6683,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45588</v>
+        <v>46202</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6688,13 +6698,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6737,7 +6742,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 28533-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6751,10 +6756,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46197</v>
+        <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6767,7 +6772,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>54.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6810,7 +6815,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6824,10 +6829,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46147</v>
+        <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6840,7 +6845,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>35.7</v>
+        <v>16.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6883,7 +6888,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6897,10 +6902,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44979</v>
+        <v>46202</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6912,13 +6917,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>10.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6961,7 +6961,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6971,14 +6971,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45162</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>6.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45436</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9.699999999999999</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7107,7 +7107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7117,14 +7117,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45042</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7136,13 +7136,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>10.7</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7185,7 +7180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7199,10 +7194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45708</v>
+        <v>44687</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7214,13 +7209,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7263,7 +7253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7273,14 +7263,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45447</v>
+        <v>45334</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7293,7 +7283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7336,7 +7326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7346,14 +7336,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44916</v>
+        <v>45236</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7365,8 +7355,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7409,7 +7404,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7419,14 +7414,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45546</v>
+        <v>45708</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7438,8 +7433,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>39.8</v>
+        <v>0.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44721</v>
+        <v>44748</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>11.8</v>
+        <v>15.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7555,7 +7555,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44687</v>
+        <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7584,8 +7584,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7628,7 +7633,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 28533-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7642,10 +7647,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45333</v>
+        <v>46197</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7658,7 +7663,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.8</v>
+        <v>54.2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7701,7 +7706,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7715,10 +7720,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44795</v>
+        <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7731,7 +7736,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>12.3</v>
+        <v>35.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7774,7 +7779,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7784,14 +7789,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45173</v>
+        <v>46265</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7803,13 +7808,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45426</v>
+        <v>46280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>62.1</v>
+        <v>54.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45387</v>
+        <v>45217</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7998,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44916</v>
+        <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8068,78 +8068,151 @@
       </c>
       <c r="V87" s="2" t="inlineStr"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
+          <t>A 34663-2025</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>45848</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>S 637-2025</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D89" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
+      <c r="E89" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>49.3</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46037</v>
+        <v>45258</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,16 +3069,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>19.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3102,49 +3102,53 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3154,14 +3158,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44958</v>
+        <v>45326</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3178,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3183,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -3201,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -3210,46 +3214,46 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3263,10 +3267,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45326</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3279,7 +3283,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3315,39 +3319,39 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
@@ -3371,7 +3375,7 @@
         <v>45405</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3459,7 +3463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3469,14 +3473,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46265</v>
+        <v>44958</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3493,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3498,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3516,7 +3520,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3529,42 +3533,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3578,10 +3582,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45645</v>
+        <v>46265</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3594,17 +3598,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3618,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3630,50 +3634,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45258</v>
+        <v>45645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19.8</v>
+        <v>4.5</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3736,10 +3736,10 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
@@ -3747,35 +3747,35 @@
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45361</v>
+        <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4011,7 +4011,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4028,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45331</v>
+        <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>11.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>44916</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4244,10 +4244,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45162</v>
+        <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4303,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45162</v>
+        <v>45217</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>51.9</v>
+        <v>1.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4376,7 +4376,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4386,14 +4386,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45293</v>
+        <v>46024</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4463,10 +4463,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45447</v>
+        <v>46037</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>31.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4522,7 +4522,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4536,10 +4536,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44979</v>
+        <v>45848</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4551,13 +4551,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4600,7 +4595,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4614,10 +4609,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46094</v>
+        <v>45848</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4630,7 +4625,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>24.5</v>
+        <v>8.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4673,7 +4668,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4687,10 +4682,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44916</v>
+        <v>45944</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4702,8 +4697,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>22.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4746,7 +4746,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45447</v>
+        <v>45776</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>15.6</v>
+        <v>27.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46108</v>
+        <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4848,13 +4848,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>20.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4897,7 +4892,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4907,14 +4902,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45333</v>
+        <v>45334</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4927,7 +4922,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4970,7 +4965,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4984,10 +4979,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46126</v>
+        <v>45361</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5000,7 +4995,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5043,7 +5038,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5057,10 +5052,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46092</v>
+        <v>45331</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5073,7 +5068,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>37.2</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5116,7 +5111,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5130,10 +5125,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46092</v>
+        <v>44748</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5146,7 +5141,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>18.2</v>
+        <v>15.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5189,7 +5184,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5203,10 +5198,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46092</v>
+        <v>44979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5218,8 +5213,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5272,14 +5272,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45944</v>
+        <v>45293</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5291,13 +5291,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>22.6</v>
+        <v>0.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5340,7 +5335,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5354,10 +5349,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45426</v>
+        <v>45162</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5370,7 +5365,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>62.1</v>
+        <v>51.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5413,7 +5408,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5427,10 +5422,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45777</v>
+        <v>45596</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5443,7 +5438,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5486,7 +5481,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5500,10 +5495,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45776</v>
+        <v>45447</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5516,7 +5511,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>27.3</v>
+        <v>9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5559,7 +5554,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5573,10 +5568,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>46094</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5588,13 +5583,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.6</v>
+        <v>24.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5637,7 +5627,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5647,14 +5637,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44721</v>
+        <v>45236</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,8 +5656,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>11.8</v>
+        <v>6.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5710,7 +5705,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5724,10 +5719,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44916</v>
+        <v>45447</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5740,7 +5735,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5783,7 +5778,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5793,14 +5788,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44916</v>
+        <v>46108</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5812,8 +5807,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>13.4</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>46126</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,13 +5885,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5934,7 +5929,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5944,14 +5939,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44805</v>
+        <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5964,7 +5959,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>37.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6007,7 +6002,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6021,10 +6016,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45596</v>
+        <v>46092</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6037,7 +6032,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.4</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6080,7 +6075,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 12984-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6094,10 +6089,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45447</v>
+        <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6110,7 +6105,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>18.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6153,7 +6148,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6167,10 +6162,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46024</v>
+        <v>45588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6182,8 +6177,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>10.2</v>
+        <v>3.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46037</v>
+        <v>44979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6255,8 +6255,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>31.3</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6299,7 +6304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6313,10 +6318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45042</v>
+        <v>45162</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6328,13 +6333,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>10.7</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6377,7 +6377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45546</v>
+        <v>45436</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>39.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6460,14 +6460,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45387</v>
+        <v>45042</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6479,8 +6479,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>8.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6523,7 +6528,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6533,14 +6538,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44795</v>
+        <v>45708</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6552,8 +6557,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>12.3</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6596,7 +6606,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6610,10 +6620,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45162</v>
+        <v>45447</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6626,7 +6636,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11.7</v>
+        <v>15.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6669,7 +6679,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6686,7 +6696,7 @@
         <v>46202</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6699,7 +6709,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>10.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6742,7 +6752,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6756,10 +6766,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45436</v>
+        <v>46202</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6772,7 +6782,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.699999999999999</v>
+        <v>2.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6832,7 +6842,7 @@
         <v>46199</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6888,7 +6898,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6902,10 +6912,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46202</v>
+        <v>44916</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6918,7 +6928,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>10.7</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6961,7 +6971,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6978,7 +6988,7 @@
         <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6991,7 +7001,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7034,7 +7044,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7051,7 +7061,7 @@
         <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7064,7 +7074,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7107,7 +7117,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7124,7 +7134,7 @@
         <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7137,7 +7147,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>6.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7180,7 +7190,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7190,14 +7200,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44687</v>
+        <v>45546</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7210,7 +7220,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.5</v>
+        <v>39.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7253,7 +7263,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7263,14 +7273,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45334</v>
+        <v>44721</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7283,7 +7293,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.4</v>
+        <v>11.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7326,7 +7336,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7340,10 +7350,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45236</v>
+        <v>44687</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7355,13 +7365,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>6.6</v>
+        <v>1.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7404,7 +7409,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7414,14 +7419,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45708</v>
+        <v>45333</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7433,13 +7438,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7482,7 +7482,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44748</v>
+        <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>15.2</v>
+        <v>12.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7572,7 +7572,7 @@
         <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 28533-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46197</v>
+        <v>45426</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>54.2</v>
+        <v>62.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46147</v>
+        <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>35.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46265</v>
+        <v>44916</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 28533-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46280</v>
+        <v>46197</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45217</v>
+        <v>46280</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>54.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7998,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45848</v>
+        <v>46147</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.4</v>
+        <v>35.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45848</v>
+        <v>46265</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 53264-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,14 +2506,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>100.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2562,230 +2562,230 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>100.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
       <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
@@ -2835,7 +2835,7 @@
         <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3049,14 +3049,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45258</v>
+        <v>44958</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,20 +3069,20 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>19.8</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -3093,55 +3093,51 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
@@ -3165,7 +3161,7 @@
         <v>45326</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3253,7 +3249,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3267,10 +3263,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>45405</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3283,7 +3279,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3319,46 +3315,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3372,10 +3368,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3388,7 +3384,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3424,46 +3420,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3473,14 +3469,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44958</v>
+        <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3493,7 +3489,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3502,10 +3498,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3520,7 +3516,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3533,42 +3529,42 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3582,10 +3578,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46265</v>
+        <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3598,16 +3594,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3622,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3634,46 +3630,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3687,10 +3687,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45645</v>
+        <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>19.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3736,10 +3736,10 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
@@ -3747,35 +3747,35 @@
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4098,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45162</v>
+        <v>45361</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4157,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4171,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44916</v>
+        <v>45331</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4240,14 +4240,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44805</v>
+        <v>45447</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4303,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4317,10 +4317,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45217</v>
+        <v>44979</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4332,8 +4332,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4376,7 +4381,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4390,10 +4395,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46024</v>
+        <v>44916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4406,7 +4411,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10.2</v>
+        <v>3.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4449,7 +4454,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4463,10 +4468,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46037</v>
+        <v>45333</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4479,7 +4484,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>31.3</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4522,7 +4527,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4536,10 +4541,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45848</v>
+        <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4552,7 +4557,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>15.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4595,7 +4600,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4609,10 +4614,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45848</v>
+        <v>45426</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4625,7 +4630,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8.4</v>
+        <v>62.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4668,7 +4673,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4682,10 +4687,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45944</v>
+        <v>46094</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4697,13 +4702,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>22.6</v>
+        <v>24.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4746,7 +4746,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45776</v>
+        <v>45848</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>27.3</v>
+        <v>8.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4819,7 +4819,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45777</v>
+        <v>45848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20.1</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4892,7 +4892,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4902,14 +4902,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45334</v>
+        <v>44979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4921,8 +4921,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4965,7 +4970,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4975,14 +4980,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45361</v>
+        <v>46108</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4994,8 +4999,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>8.4</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5038,7 +5048,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5052,10 +5062,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45331</v>
+        <v>44721</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5068,7 +5078,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.9</v>
+        <v>11.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5111,7 +5121,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5125,10 +5135,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44748</v>
+        <v>44916</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5141,7 +5151,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>15.2</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5184,7 +5194,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5198,10 +5208,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44979</v>
+        <v>44916</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5213,13 +5223,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>13.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5262,7 +5267,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5272,14 +5277,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45293</v>
+        <v>46126</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5292,7 +5297,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5335,7 +5340,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5349,10 +5354,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45162</v>
+        <v>46092</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5365,7 +5370,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>51.9</v>
+        <v>37.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5408,7 +5413,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 12984-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5422,10 +5427,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45596</v>
+        <v>46092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5438,7 +5443,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>17.4</v>
+        <v>18.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5481,7 +5486,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5495,10 +5500,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45447</v>
+        <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5511,7 +5516,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5554,7 +5559,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5568,10 +5573,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46094</v>
+        <v>45588</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5583,8 +5588,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>24.5</v>
+        <v>3.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5627,7 +5637,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5641,10 +5651,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45236</v>
+        <v>44805</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5656,13 +5666,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5705,7 +5710,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5719,10 +5724,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45447</v>
+        <v>45944</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5734,8 +5739,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>22.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5778,7 +5788,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5788,14 +5798,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46108</v>
+        <v>45546</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5807,13 +5817,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>39.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5856,7 +5861,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5870,10 +5875,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46126</v>
+        <v>45387</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5886,7 +5891,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5929,7 +5934,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5943,10 +5948,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46092</v>
+        <v>45162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5959,7 +5964,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>37.2</v>
+        <v>11.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6002,7 +6007,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6016,10 +6021,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46092</v>
+        <v>45436</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6032,7 +6037,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6075,7 +6080,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6089,10 +6094,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46092</v>
+        <v>45777</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6105,7 +6110,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>18.2</v>
+        <v>20.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6148,7 +6153,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6162,10 +6167,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45588</v>
+        <v>45776</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,13 +6182,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>3.7</v>
+        <v>27.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44979</v>
+        <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6255,13 +6255,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6304,7 +6299,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6314,14 +6309,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45162</v>
+        <v>46202</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6334,7 +6329,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6377,7 +6372,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6391,10 +6386,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45436</v>
+        <v>44748</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6407,7 +6402,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9.699999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6450,7 +6445,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6460,14 +6455,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45042</v>
+        <v>46199</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6479,13 +6474,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>10.7</v>
+        <v>16.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6528,7 +6518,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6542,10 +6532,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45708</v>
+        <v>45162</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6557,13 +6547,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6606,7 +6591,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6620,10 +6605,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45447</v>
+        <v>46202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6636,7 +6621,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15.6</v>
+        <v>10.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6679,7 +6664,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6693,10 +6678,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6709,7 +6694,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>10.7</v>
+        <v>6.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6752,7 +6737,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6766,10 +6751,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46202</v>
+        <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6782,7 +6767,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>51.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6825,7 +6810,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6839,10 +6824,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6855,7 +6840,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>16.9</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6898,7 +6883,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6912,10 +6897,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44916</v>
+        <v>46210</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6928,7 +6913,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6971,7 +6956,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6981,14 +6966,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>45293</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7001,7 +6986,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7044,7 +7029,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7058,10 +7043,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>45596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7074,7 +7059,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>17.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7117,7 +7102,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7131,10 +7116,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>45447</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,7 +7132,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7190,7 +7175,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7204,10 +7189,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45546</v>
+        <v>46024</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7220,7 +7205,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>39.8</v>
+        <v>10.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7263,7 +7248,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 28533-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,10 +7262,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44721</v>
+        <v>46197</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7293,7 +7278,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>11.8</v>
+        <v>54.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7336,7 +7321,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7346,14 +7331,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44687</v>
+        <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7366,7 +7351,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7409,7 +7394,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7423,10 +7408,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45333</v>
+        <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7439,7 +7424,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>35.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7482,7 +7467,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7496,10 +7481,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44795</v>
+        <v>46280</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7512,7 +7497,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>12.3</v>
+        <v>54.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7555,7 +7540,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7565,14 +7550,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45173</v>
+        <v>46037</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7584,13 +7569,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7633,7 +7613,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7643,14 +7623,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45426</v>
+        <v>45042</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7662,8 +7642,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>62.1</v>
+        <v>10.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7691,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7720,10 +7705,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45387</v>
+        <v>44795</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7736,7 +7721,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>12.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7764,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7789,14 +7774,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44916</v>
+        <v>45334</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7794,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7837,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28533-2026</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7862,14 +7847,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46197</v>
+        <v>45236</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7881,8 +7866,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>54.2</v>
+        <v>6.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7925,7 +7915,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7935,14 +7925,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46280</v>
+        <v>45708</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7954,8 +7944,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>54.2</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7993,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8008,14 +8003,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46147</v>
+        <v>45173</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8027,8 +8022,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>35.7</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46265</v>
+        <v>45217</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U2" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,6 @@
 Späd brosklav
 Blodticka
 Bårdlav
-Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -782,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +908,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1039,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1161,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1280,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1403,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1517,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1630,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1744,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1852,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1943,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1957,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1973,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2009,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2400,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2495,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53264-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,14 +2505,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,23 +2525,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>100.3</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2550,10 +2549,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2562,150 +2561,150 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
@@ -2729,7 +2728,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2835,7 +2834,7 @@
         <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2945,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3038,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3049,14 +3048,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44958</v>
+        <v>45326</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,7 +3068,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3078,10 +3077,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -3096,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -3105,46 +3104,46 @@
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3158,10 +3157,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45326</v>
+        <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,7 +3173,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3214,42 +3213,42 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3263,10 +3262,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45405</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3279,7 +3278,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3315,46 +3314,46 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3364,14 +3363,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46265</v>
+        <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3383,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3393,10 +3392,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3411,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3424,42 +3423,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3473,10 +3472,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46037</v>
+        <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3529,35 +3528,35 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
@@ -3581,7 +3580,7 @@
         <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3690,7 +3689,7 @@
         <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3798,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3876,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3954,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4028,7 +4027,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4084,7 +4083,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4097,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45361</v>
+        <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4113,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4156,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4170,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45331</v>
+        <v>44916</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4186,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4229,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4240,14 +4239,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45447</v>
+        <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4259,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4302,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4313,14 +4312,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44979</v>
+        <v>45334</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4332,13 +4331,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4381,7 +4375,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4395,10 +4389,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44916</v>
+        <v>45361</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4411,7 +4405,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.2</v>
+        <v>8.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4454,7 +4448,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4468,10 +4462,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45333</v>
+        <v>45331</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4484,7 +4478,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4527,7 +4521,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4541,10 +4535,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45447</v>
+        <v>44748</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4557,7 +4551,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4600,7 +4594,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4614,10 +4608,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45426</v>
+        <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4629,8 +4623,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>62.1</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4673,7 +4672,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4683,14 +4682,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46094</v>
+        <v>45293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4703,7 +4702,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>24.5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4746,7 +4745,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4760,10 +4759,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45848</v>
+        <v>45162</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4776,7 +4775,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>8.4</v>
+        <v>51.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4819,7 +4818,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4829,14 +4828,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45848</v>
+        <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4848,8 +4847,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4892,7 +4896,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4906,10 +4910,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44979</v>
+        <v>45447</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4921,13 +4925,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4970,7 +4969,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4980,14 +4979,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46108</v>
+        <v>45944</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5001,11 +5000,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.7</v>
+        <v>22.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5048,7 +5047,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5062,10 +5061,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44721</v>
+        <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5078,7 +5077,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>11.8</v>
+        <v>27.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5121,7 +5120,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5135,10 +5134,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44916</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5151,7 +5150,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.2</v>
+        <v>20.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5194,7 +5193,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5208,10 +5207,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44916</v>
+        <v>45588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5223,8 +5222,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>13.4</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5267,7 +5271,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5281,10 +5285,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46126</v>
+        <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5297,7 +5301,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>17.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5340,7 +5344,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5354,10 +5358,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46092</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5369,8 +5373,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>37.2</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5413,7 +5422,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5427,10 +5436,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46092</v>
+        <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5443,7 +5452,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>18.2</v>
+        <v>9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5486,7 +5495,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5500,10 +5509,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46092</v>
+        <v>46024</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5516,7 +5525,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>10.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5559,7 +5568,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5569,14 +5578,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45588</v>
+        <v>45162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5588,13 +5597,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5637,7 +5641,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5647,14 +5651,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44805</v>
+        <v>46037</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5667,7 +5671,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>31.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5710,7 +5714,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5724,10 +5728,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45944</v>
+        <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,13 +5743,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5788,7 +5787,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5798,14 +5797,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45546</v>
+        <v>45042</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5817,8 +5816,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>39.8</v>
+        <v>10.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5861,7 +5865,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5875,10 +5879,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45387</v>
+        <v>46094</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5891,7 +5895,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>8.199999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5934,7 +5938,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5944,14 +5948,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45162</v>
+        <v>45708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5963,8 +5967,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>11.7</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6007,7 +6016,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6017,14 +6026,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45436</v>
+        <v>46108</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6036,8 +6045,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>9.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6080,7 +6094,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6094,10 +6108,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45777</v>
+        <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6110,7 +6124,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>20.1</v>
+        <v>15.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6153,7 +6167,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6167,10 +6181,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45776</v>
+        <v>46126</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6183,7 +6197,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>27.3</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6226,7 +6240,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6236,14 +6250,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44687</v>
+        <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6256,7 +6270,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.5</v>
+        <v>37.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6299,7 +6313,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6313,10 +6327,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46202</v>
+        <v>46092</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6329,7 +6343,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6372,7 +6386,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 12984-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6386,10 +6400,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44748</v>
+        <v>46092</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6402,7 +6416,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>15.2</v>
+        <v>18.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6445,7 +6459,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6459,10 +6473,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46199</v>
+        <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6475,7 +6489,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>16.9</v>
+        <v>7.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6518,7 +6532,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6528,14 +6542,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45162</v>
+        <v>45546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6548,7 +6562,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>39.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6608,7 +6622,7 @@
         <v>46202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6664,7 +6678,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6678,10 +6692,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6694,7 +6708,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6737,7 +6751,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6751,10 +6765,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45162</v>
+        <v>46199</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6767,7 +6781,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>51.9</v>
+        <v>16.9</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6810,7 +6824,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6824,10 +6838,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46210</v>
+        <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6840,7 +6854,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6883,7 +6897,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6893,14 +6907,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46210</v>
+        <v>44687</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6913,7 +6927,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6956,7 +6970,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,14 +6980,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45293</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6986,7 +7000,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7029,7 +7043,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7043,10 +7057,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45596</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7059,7 +7073,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>17.4</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7102,7 +7116,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7116,10 +7130,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45447</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7132,7 +7146,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7175,7 +7189,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7189,10 +7203,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46024</v>
+        <v>45333</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7205,7 +7219,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>10.2</v>
+        <v>1.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7248,7 +7262,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 28533-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7262,10 +7276,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46197</v>
+        <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7278,7 +7292,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>54.2</v>
+        <v>12.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7321,7 +7335,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7331,14 +7345,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46265</v>
+        <v>45173</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7350,8 +7364,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7394,7 +7413,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7408,10 +7427,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46147</v>
+        <v>45426</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7424,7 +7443,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>35.7</v>
+        <v>62.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7467,7 +7486,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7481,10 +7500,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46280</v>
+        <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7497,7 +7516,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>54.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7540,7 +7559,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7554,10 +7573,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46037</v>
+        <v>44916</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7570,7 +7589,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>31.3</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7613,7 +7632,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7623,14 +7642,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45042</v>
+        <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7642,13 +7661,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>10.7</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7691,7 +7705,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7705,10 +7719,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44795</v>
+        <v>46280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7721,7 +7735,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>12.3</v>
+        <v>54.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7764,7 +7778,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7774,14 +7788,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45334</v>
+        <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7794,7 +7808,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7837,7 +7851,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7847,14 +7861,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45236</v>
+        <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7866,13 +7880,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>6.6</v>
+        <v>35.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7915,7 +7924,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7925,14 +7934,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45708</v>
+        <v>45848</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7944,13 +7953,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7993,7 +7997,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8003,14 +8007,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45173</v>
+        <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8022,13 +8026,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8068,27 +8067,27 @@
       </c>
       <c r="V87" s="2" t="inlineStr"/>
     </row>
-    <row r="88" ht="15" customHeight="1">
+    <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>S 637-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45217</v>
+        <v>45714</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8101,7 +8100,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>49.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8140,79 +8139,6 @@
         <v>0</v>
       </c>
       <c r="V88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>S 637-2025</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Späd brosklav
 Blodticka
 Bårdlav
+Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -781,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -908,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1161,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1403,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1630,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1744,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1852,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1960,7 +1961,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2071,7 +2072,7 @@
         <v>45447</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2182,7 +2183,7 @@
         <v>45779</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2294,7 @@
         <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2400,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2512,7 +2513,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2622,7 +2623,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2728,7 +2729,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2834,7 +2835,7 @@
         <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2945,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3055,7 +3056,7 @@
         <v>45326</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3160,7 +3161,7 @@
         <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3265,7 +3266,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3371,7 @@
         <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3475,7 +3476,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3580,7 +3581,7 @@
         <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3690,7 @@
         <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3798,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3876,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,7 +3955,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4027,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4100,7 +4101,7 @@
         <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4173,7 +4174,7 @@
         <v>44916</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4246,7 +4247,7 @@
         <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4319,7 +4320,7 @@
         <v>45334</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4392,7 +4393,7 @@
         <v>45361</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4465,7 +4466,7 @@
         <v>45331</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4538,7 +4539,7 @@
         <v>44748</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4611,7 +4612,7 @@
         <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4689,7 +4690,7 @@
         <v>45293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4762,7 +4763,7 @@
         <v>45162</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4835,7 +4836,7 @@
         <v>45236</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4913,7 +4914,7 @@
         <v>45447</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4986,7 +4987,7 @@
         <v>45944</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5064,7 +5065,7 @@
         <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5137,7 +5138,7 @@
         <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5210,7 +5211,7 @@
         <v>45588</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5288,7 +5289,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5361,7 +5362,7 @@
         <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5439,7 +5440,7 @@
         <v>45447</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5512,7 +5513,7 @@
         <v>46024</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5585,7 +5586,7 @@
         <v>45162</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5658,7 +5659,7 @@
         <v>46037</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5731,7 +5732,7 @@
         <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5804,7 +5805,7 @@
         <v>45042</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5882,7 +5883,7 @@
         <v>46094</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5955,7 +5956,7 @@
         <v>45708</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6033,7 +6034,7 @@
         <v>46108</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6111,7 +6112,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6184,7 +6185,7 @@
         <v>46126</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6257,7 +6258,7 @@
         <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6330,7 +6331,7 @@
         <v>46092</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6403,7 +6404,7 @@
         <v>46092</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6476,7 +6477,7 @@
         <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6549,7 +6550,7 @@
         <v>45546</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6622,7 +6623,7 @@
         <v>46202</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6695,7 +6696,7 @@
         <v>46202</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6768,7 +6769,7 @@
         <v>46199</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6841,7 +6842,7 @@
         <v>44721</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6914,7 +6915,7 @@
         <v>44687</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6987,7 +6988,7 @@
         <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7060,7 +7061,7 @@
         <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7133,7 +7134,7 @@
         <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7206,7 +7207,7 @@
         <v>45333</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7279,7 +7280,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7352,7 +7353,7 @@
         <v>45173</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7430,7 +7431,7 @@
         <v>45426</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7503,7 +7504,7 @@
         <v>45387</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7576,7 +7577,7 @@
         <v>44916</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7649,7 +7650,7 @@
         <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7722,7 +7723,7 @@
         <v>46280</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7795,7 +7796,7 @@
         <v>45217</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7868,7 +7869,7 @@
         <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7941,7 +7942,7 @@
         <v>45848</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8014,7 +8015,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8087,7 +8088,7 @@
         <v>45714</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1961,7 +1961,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>45447</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>45779</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45222</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45326</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>44916</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45334</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>45361</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>45331</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>44748</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
         <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45162</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45236</v>
+        <v>45944</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4850,11 +4850,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4897,7 +4897,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45447</v>
+        <v>45776</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>27.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45944</v>
+        <v>45777</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4999,13 +4999,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>22.6</v>
+        <v>20.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5048,7 +5043,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5058,14 +5053,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45776</v>
+        <v>45236</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5077,8 +5072,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>27.3</v>
+        <v>6.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>45447</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20.1</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45588</v>
+        <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5223,13 +5223,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>17.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5272,7 +5267,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5286,10 +5281,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45596</v>
+        <v>45447</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5302,7 +5297,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>17.4</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5345,7 +5340,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5359,10 +5354,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>46024</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5374,13 +5369,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>10.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5423,7 +5413,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5437,10 +5427,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45447</v>
+        <v>45588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5452,8 +5442,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5496,7 +5491,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5510,10 +5505,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46024</v>
+        <v>46037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5526,7 +5521,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>10.2</v>
+        <v>31.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5569,7 +5564,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5579,14 +5574,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45162</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5598,8 +5593,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5642,7 +5642,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5652,14 +5652,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46037</v>
+        <v>45162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>31.3</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5729,10 +5729,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45436</v>
+        <v>46094</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9.699999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5788,7 +5788,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5798,14 +5798,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45042</v>
+        <v>45436</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5817,13 +5817,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5866,7 +5861,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5876,14 +5871,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46094</v>
+        <v>46108</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5895,8 +5890,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>24.5</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5939,7 +5939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5949,14 +5949,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45708</v>
+        <v>46202</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5968,13 +5968,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.8</v>
+        <v>10.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6017,7 +6012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6027,14 +6022,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46108</v>
+        <v>46202</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6046,13 +6041,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6095,7 +6085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6109,10 +6099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45447</v>
+        <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6125,7 +6115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>15.6</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6168,7 +6158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6198,7 +6188,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>37.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6241,7 +6231,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6258,7 +6248,7 @@
         <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6271,7 +6261,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>37.2</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6314,7 +6304,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6328,10 +6318,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46092</v>
+        <v>46199</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6344,7 +6334,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>16.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6387,7 +6377,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12984-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6401,10 +6391,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46092</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6417,7 +6407,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>18.2</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6460,7 +6450,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6474,10 +6464,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44916</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6490,7 +6480,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6533,7 +6523,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6547,10 +6537,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6563,7 +6553,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>39.8</v>
+        <v>6.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6606,7 +6596,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,14 +6606,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46202</v>
+        <v>45042</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6633,6 +6623,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -6679,7 +6674,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6689,14 +6684,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46202</v>
+        <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6708,8 +6703,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46199</v>
+        <v>45447</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>16.9</v>
+        <v>15.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44721</v>
+        <v>44916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>11.8</v>
+        <v>7.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6898,7 +6898,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6908,14 +6908,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44687</v>
+        <v>45546</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.5</v>
+        <v>39.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6985,10 +6985,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>44721</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>11.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7044,7 +7044,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7054,14 +7054,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>44687</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7117,7 +7117,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7131,10 +7131,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>46265</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7207,7 +7207,7 @@
         <v>45333</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,10 +7277,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44795</v>
+        <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>12.3</v>
+        <v>54.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7336,7 +7336,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7346,14 +7346,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45173</v>
+        <v>44795</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7365,13 +7365,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7414,7 +7409,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7428,10 +7423,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45426</v>
+        <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7444,7 +7439,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>62.1</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7487,7 +7482,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7497,14 +7492,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45387</v>
+        <v>45173</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7516,8 +7511,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>8.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7560,7 +7560,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7574,10 +7574,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44916</v>
+        <v>45426</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3.2</v>
+        <v>62.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46265</v>
+        <v>46147</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.7</v>
+        <v>35.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46280</v>
+        <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>54.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45217</v>
+        <v>44916</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46147</v>
+        <v>45217</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>35.7</v>
+        <v>1.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7942,7 +7942,7 @@
         <v>45848</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>45714</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE88"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 53264-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,14 +2506,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>45222</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>100.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2562,367 +2562,367 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45326</v>
+        <v>45645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,16 +3069,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3109,42 +3109,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3158,10 +3162,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45405</v>
+        <v>45258</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,16 +3178,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>19.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3198,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3207,49 +3211,53 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3259,14 +3267,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>44958</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3279,7 +3287,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3288,10 +3296,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3306,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3319,42 +3327,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3364,14 +3372,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44958</v>
+        <v>45326</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3384,7 +3392,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3393,10 +3401,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3411,7 +3419,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3420,46 +3428,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3473,10 +3481,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46265</v>
+        <v>45405</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3497,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3525,46 +3533,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3578,10 +3586,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3594,17 +3602,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3618,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3630,50 +3638,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3687,10 +3691,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45258</v>
+        <v>46265</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,17 +3707,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19.8</v>
+        <v>6.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3727,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3736,46 +3740,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>45588</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3967,8 +3967,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4011,7 +4016,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4021,14 +4026,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44623</v>
+        <v>44805</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4041,7 +4046,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4084,7 +4089,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4103,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45162</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4119,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.7</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4162,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4176,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44916</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4192,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4235,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4240,14 +4245,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44805</v>
+        <v>45361</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4265,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>8.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4308,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4313,14 +4318,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45334</v>
+        <v>45331</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4333,7 +4338,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4376,7 +4381,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4390,10 +4395,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45361</v>
+        <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4406,7 +4411,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4449,7 +4454,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4463,10 +4468,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45331</v>
+        <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4479,7 +4484,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4522,7 +4527,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4536,10 +4541,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44748</v>
+        <v>44979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4551,8 +4556,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>15.2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4595,7 +4605,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4609,10 +4619,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44979</v>
+        <v>45546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4624,13 +4634,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>39.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4673,7 +4678,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4683,14 +4688,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45293</v>
+        <v>45387</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4703,7 +4708,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4746,7 +4751,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4763,7 +4768,7 @@
         <v>45162</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4776,7 +4781,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>51.9</v>
+        <v>11.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4819,7 +4824,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4833,10 +4838,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45944</v>
+        <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4848,13 +4853,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>22.6</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4897,7 +4897,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45776</v>
+        <v>45447</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>27.3</v>
+        <v>15.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4984,10 +4984,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45777</v>
+        <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>20.1</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5043,7 +5043,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5053,14 +5053,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45236</v>
+        <v>45436</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5072,13 +5072,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>6.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5121,7 +5116,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5135,10 +5130,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45447</v>
+        <v>45944</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5150,8 +5145,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>6</v>
+        <v>22.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45596</v>
+        <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>17.4</v>
+        <v>62.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45447</v>
+        <v>45777</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>20.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46024</v>
+        <v>45776</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.2</v>
+        <v>27.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45588</v>
+        <v>44687</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5442,13 +5442,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5491,7 +5486,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5505,10 +5500,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46037</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,8 +5515,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>31.3</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>44748</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,13 +5593,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5659,7 +5654,7 @@
         <v>45162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5715,7 +5710,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5729,10 +5724,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46094</v>
+        <v>44721</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5745,7 +5740,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>24.5</v>
+        <v>11.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5788,7 +5783,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5802,10 +5797,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45436</v>
+        <v>44916</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5818,7 +5813,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5861,7 +5856,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5871,14 +5866,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46108</v>
+        <v>44916</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5890,13 +5885,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>13.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5939,7 +5929,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5953,10 +5943,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46202</v>
+        <v>45162</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5969,7 +5959,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.7</v>
+        <v>51.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6012,7 +6002,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6026,10 +6016,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46202</v>
+        <v>46024</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6042,7 +6032,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.3</v>
+        <v>10.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6085,7 +6075,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6099,10 +6089,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46126</v>
+        <v>45596</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6115,7 +6105,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>17.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6158,7 +6148,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6172,10 +6162,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6188,7 +6178,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>37.2</v>
+        <v>9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6231,7 +6221,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6245,10 +6235,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46092</v>
+        <v>46037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6261,7 +6251,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>31.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6304,7 +6294,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6314,14 +6304,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46199</v>
+        <v>45293</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6334,7 +6324,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>16.9</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6377,7 +6367,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6391,10 +6381,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>46280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6407,7 +6397,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>54.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6450,7 +6440,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6464,10 +6454,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>46288</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6480,7 +6470,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>13.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6523,7 +6513,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6537,10 +6527,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46210</v>
+        <v>46287</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6553,7 +6543,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6596,7 +6586,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6606,14 +6596,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45042</v>
+        <v>46147</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6625,13 +6615,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>10.7</v>
+        <v>35.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6674,7 +6659,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6684,14 +6669,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45708</v>
+        <v>45848</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6703,13 +6688,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6752,7 +6732,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6766,10 +6746,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45447</v>
+        <v>45848</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6782,7 +6762,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15.6</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6825,7 +6805,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6839,10 +6819,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44916</v>
+        <v>46094</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6855,7 +6835,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.2</v>
+        <v>24.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6898,7 +6878,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6908,14 +6888,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45546</v>
+        <v>45042</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6927,8 +6907,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>39.8</v>
+        <v>10.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6971,7 +6956,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6981,14 +6966,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44721</v>
+        <v>46108</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7000,8 +6985,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>11.8</v>
+        <v>1.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7044,7 +7034,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7054,14 +7044,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44687</v>
+        <v>46126</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7074,7 +7064,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.5</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7117,7 +7107,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7131,10 +7121,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46265</v>
+        <v>46092</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7147,7 +7137,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>37.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7190,7 +7180,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7204,10 +7194,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45333</v>
+        <v>46092</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7220,7 +7210,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7263,7 +7253,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7277,10 +7267,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46280</v>
+        <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7293,7 +7283,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>54.2</v>
+        <v>12.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7336,7 +7326,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7346,14 +7336,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44795</v>
+        <v>45334</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7366,7 +7356,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>12.3</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7409,7 +7399,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7419,14 +7409,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46287</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7438,8 +7428,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7482,7 +7477,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7496,10 +7491,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45173</v>
+        <v>45708</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7513,11 +7508,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7560,7 +7555,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7570,14 +7565,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45426</v>
+        <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7589,8 +7584,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>62.1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46147</v>
+        <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>35.7</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45387</v>
+        <v>46199</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8.199999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44916</v>
+        <v>46202</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>3.2</v>
+        <v>10.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45217</v>
+        <v>46210</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45848</v>
+        <v>46210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7998,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45848</v>
+        <v>46210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8068,78 +8068,151 @@
       </c>
       <c r="V87" s="2" t="inlineStr"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
+          <t>A 35765-2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>S 637-2025</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D88" s="1" t="n">
+      <c r="D89" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="E88" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
+      <c r="E89" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
         <v>49.3</v>
       </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" s="2" t="inlineStr"/>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1974,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2010,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2401,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 53264-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,14 +2506,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45222</v>
+        <v>44896</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2526,23 +2526,23 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>100.3</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
@@ -2550,10 +2550,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2562,367 +2562,367 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>100.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 17740-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45035</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>20.1</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45645</v>
+        <v>45326</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,17 +3069,17 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3109,46 +3109,42 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3162,10 +3158,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45258</v>
+        <v>45405</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3178,17 +3174,17 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>19.8</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
@@ -3202,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3211,53 +3207,49 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3267,14 +3259,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44958</v>
+        <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3287,7 +3279,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3296,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -3314,7 +3306,7 @@
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3327,42 +3319,42 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3372,14 +3364,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45326</v>
+        <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3392,7 +3384,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3401,10 +3393,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3419,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3428,46 +3420,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3481,10 +3473,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3497,7 +3489,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3533,46 +3525,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3586,10 +3578,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46037</v>
+        <v>45645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3602,16 +3594,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3626,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3638,46 +3630,50 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3691,10 +3687,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46265</v>
+        <v>45258</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3707,16 +3703,16 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.1</v>
+        <v>19.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3731,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3740,42 +3736,46 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45588</v>
+        <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3967,13 +3967,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4016,7 +4011,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4026,14 +4021,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44805</v>
+        <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4046,7 +4041,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4089,7 +4084,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4103,10 +4098,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4119,7 +4114,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>11.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4162,7 +4157,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4176,10 +4171,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44623</v>
+        <v>44916</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4192,7 +4187,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4235,7 +4230,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4245,14 +4240,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45361</v>
+        <v>44805</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4265,7 +4260,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8.4</v>
+        <v>3.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4308,7 +4303,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4318,14 +4313,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45331</v>
+        <v>45334</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4338,7 +4333,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4381,7 +4376,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4395,10 +4390,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45217</v>
+        <v>45361</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4411,7 +4406,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4454,7 +4449,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4468,10 +4463,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45447</v>
+        <v>45331</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4484,7 +4479,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4527,7 +4522,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4541,10 +4536,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44979</v>
+        <v>44748</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4556,13 +4551,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4605,7 +4595,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4619,10 +4609,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45546</v>
+        <v>44979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4634,8 +4624,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>39.8</v>
+        <v>4.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4678,7 +4673,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4688,14 +4683,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45387</v>
+        <v>45293</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4708,7 +4703,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4751,7 +4746,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4768,7 +4763,7 @@
         <v>45162</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4781,7 +4776,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>11.7</v>
+        <v>51.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4824,7 +4819,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4838,10 +4833,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44916</v>
+        <v>45944</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4853,8 +4848,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>22.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4897,7 +4897,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4907,14 +4907,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45447</v>
+        <v>45236</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4926,8 +4926,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>15.6</v>
+        <v>6.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4970,7 +4975,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4984,10 +4989,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45333</v>
+        <v>45447</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5000,7 +5005,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5043,7 +5048,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45436</v>
+        <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5073,7 +5078,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9.699999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5116,7 +5121,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5130,10 +5135,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45944</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5145,13 +5150,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>22.6</v>
+        <v>20.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5194,7 +5194,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45426</v>
+        <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>62.1</v>
+        <v>17.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5267,7 +5267,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5281,10 +5281,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45777</v>
+        <v>45447</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>20.1</v>
+        <v>9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5354,10 +5354,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45776</v>
+        <v>46024</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>27.3</v>
+        <v>10.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5413,7 +5413,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5423,14 +5423,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44687</v>
+        <v>45588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5442,8 +5442,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5486,7 +5491,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5500,10 +5505,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>46037</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5515,13 +5520,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>31.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5564,7 +5564,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44748</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,8 +5593,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>15.2</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5654,7 +5659,7 @@
         <v>45162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5710,7 +5715,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5724,10 +5729,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44721</v>
+        <v>46094</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5740,7 +5745,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>11.8</v>
+        <v>24.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5783,7 +5788,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5797,10 +5802,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44916</v>
+        <v>45436</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5813,7 +5818,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5856,7 +5861,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5866,14 +5871,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44916</v>
+        <v>46108</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5885,8 +5890,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>13.4</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5929,7 +5939,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5943,10 +5953,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45162</v>
+        <v>46126</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5959,7 +5969,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>51.9</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6002,7 +6012,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6016,10 +6026,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46024</v>
+        <v>46092</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6032,7 +6042,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>10.2</v>
+        <v>37.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6075,7 +6085,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6089,10 +6099,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45596</v>
+        <v>46092</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6105,7 +6115,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>17.4</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6148,7 +6158,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6158,14 +6168,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45447</v>
+        <v>45042</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6177,8 +6187,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6221,7 +6236,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6231,14 +6246,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46037</v>
+        <v>45708</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6250,8 +6265,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>31.3</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6294,7 +6314,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6304,14 +6324,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45293</v>
+        <v>45447</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6324,7 +6344,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>15.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6367,7 +6387,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6381,10 +6401,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46280</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6397,7 +6417,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>54.2</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6440,7 +6460,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6454,10 +6474,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46288</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6470,7 +6490,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>13.6</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6513,7 +6533,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6527,10 +6547,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6543,7 +6563,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6586,7 +6606,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6600,10 +6620,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46147</v>
+        <v>44916</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6616,7 +6636,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>35.7</v>
+        <v>7.2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6659,7 +6679,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6673,10 +6693,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45848</v>
+        <v>45546</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6689,7 +6709,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.4</v>
+        <v>39.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6732,7 +6752,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6746,10 +6766,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45848</v>
+        <v>44721</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6762,7 +6782,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>11.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6805,7 +6825,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6815,14 +6835,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46094</v>
+        <v>44687</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6835,7 +6855,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>24.5</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6878,7 +6898,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6888,14 +6908,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45042</v>
+        <v>45333</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6907,13 +6927,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>10.7</v>
+        <v>1.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6956,7 +6971,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,14 +6981,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46108</v>
+        <v>44795</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6985,13 +7000,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.7</v>
+        <v>12.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7034,7 +7044,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7044,14 +7054,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46126</v>
+        <v>45173</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7063,8 +7073,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7107,7 +7122,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7121,10 +7136,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46092</v>
+        <v>45426</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7137,7 +7152,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>37.2</v>
+        <v>62.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7180,7 +7195,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7194,10 +7209,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46092</v>
+        <v>46265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7210,7 +7225,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7253,7 +7268,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7267,10 +7282,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44795</v>
+        <v>45387</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7283,7 +7298,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>12.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7326,7 +7341,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7336,14 +7351,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45334</v>
+        <v>44916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7356,7 +7371,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7399,7 +7414,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7409,14 +7424,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45236</v>
+        <v>46280</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7428,13 +7443,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>6.6</v>
+        <v>54.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7477,7 +7487,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7487,14 +7497,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45708</v>
+        <v>46287</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7506,13 +7516,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7555,7 +7560,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7565,14 +7570,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45173</v>
+        <v>46147</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7584,13 +7589,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.3</v>
+        <v>35.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7650,7 +7650,7 @@
         <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>10.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7720,10 +7720,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>16.9</v>
+        <v>2.3</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7779,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>10.7</v>
+        <v>16.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7852,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46210</v>
+        <v>46288</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>6.8</v>
+        <v>13.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7925,7 +7925,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7939,10 +7939,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46210</v>
+        <v>45217</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7998,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46210</v>
+        <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8085,10 +8085,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46265</v>
+        <v>45848</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>8.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U2" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,6 @@
 Späd brosklav
 Blodticka
 Bårdlav
-Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -782,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -909,7 +908,7 @@
         <v>45426</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1039,7 @@
         <v>46244</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1162,7 +1161,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1281,7 +1280,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1404,7 +1403,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1518,7 +1517,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1631,7 +1630,7 @@
         <v>45775</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1744,7 @@
         <v>46170</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1853,7 +1852,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1944,7 +1943,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1958,10 +1957,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,16 +1973,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1998,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -2010,374 +2009,374 @@
         <v>3</v>
       </c>
       <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE13">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2401,7 +2400,7 @@
         <v>45776</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2496,7 +2495,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 17740-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2506,14 +2505,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44896</v>
+        <v>45035</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2525,23 +2524,28 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>20.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2553,7 +2557,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
@@ -2562,367 +2566,362 @@
         <v>2</v>
       </c>
       <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE18">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>100.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
@@ -2946,7 +2945,7 @@
         <v>44844</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3039,7 +3038,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3053,10 +3052,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45326</v>
+        <v>45645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3069,16 +3068,16 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3093,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3109,42 +3108,46 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3158,10 +3161,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45405</v>
+        <v>45258</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3174,16 +3177,16 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>19.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -3198,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -3207,42 +3210,46 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE24">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3266,7 +3273,7 @@
         <v>46037</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3371,7 +3378,7 @@
         <v>44958</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3459,7 +3466,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3473,10 +3480,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46265</v>
+        <v>45326</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3489,7 +3496,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3525,46 +3532,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3578,10 +3585,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45645</v>
+        <v>45405</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3594,17 +3601,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3618,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3634,46 +3641,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3687,10 +3690,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45258</v>
+        <v>46265</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3703,17 +3706,17 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>19.8</v>
+        <v>6.1</v>
       </c>
       <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -3727,7 +3730,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3736,46 +3739,42 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
@@ -3799,7 +3798,7 @@
         <v>44840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3877,7 +3876,7 @@
         <v>44875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3955,7 +3954,7 @@
         <v>44623</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4028,7 +4027,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4084,7 +4083,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4098,10 +4097,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45162</v>
+        <v>45361</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4114,7 +4113,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4157,7 +4156,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4171,10 +4170,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44916</v>
+        <v>45331</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4187,7 +4186,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4230,7 +4229,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4240,14 +4239,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44805</v>
+        <v>46024</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4260,7 +4259,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.1</v>
+        <v>10.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4303,7 +4302,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4313,14 +4312,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45334</v>
+        <v>45447</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4333,7 +4332,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4376,7 +4375,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4390,10 +4389,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45361</v>
+        <v>45217</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4406,7 +4405,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4449,7 +4448,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4463,10 +4462,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45331</v>
+        <v>44979</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4478,8 +4477,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4522,7 +4526,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4536,10 +4540,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44748</v>
+        <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4552,7 +4556,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>15.2</v>
+        <v>31.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4595,7 +4599,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4609,10 +4613,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44979</v>
+        <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4624,13 +4628,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4673,7 +4672,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4683,14 +4682,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45293</v>
+        <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4703,7 +4702,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>15.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4746,7 +4745,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4760,10 +4759,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45162</v>
+        <v>45333</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4776,7 +4775,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>51.9</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4819,7 +4818,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4833,10 +4832,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45944</v>
+        <v>46094</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4848,13 +4847,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>22.6</v>
+        <v>24.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4897,7 +4891,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4907,14 +4901,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45236</v>
+        <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4928,11 +4922,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>6.6</v>
+        <v>22.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4975,7 +4969,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4989,10 +4983,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45447</v>
+        <v>45426</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5005,7 +4999,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>62.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5048,7 +5042,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5058,14 +5052,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45776</v>
+        <v>46108</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5077,8 +5071,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>27.3</v>
+        <v>1.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5138,7 +5137,7 @@
         <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5194,7 +5193,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5208,10 +5207,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45596</v>
+        <v>45776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5224,7 +5223,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>17.4</v>
+        <v>27.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5267,7 +5266,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5281,10 +5280,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45447</v>
+        <v>44979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5296,8 +5295,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>4.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5340,7 +5344,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5354,10 +5358,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46024</v>
+        <v>46126</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5370,7 +5374,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5413,7 +5417,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5427,10 +5431,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45588</v>
+        <v>46092</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5442,13 +5446,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>37.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5491,7 +5490,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5505,10 +5504,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46037</v>
+        <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5521,7 +5520,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>31.3</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5564,7 +5563,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5578,10 +5577,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,13 +5592,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5642,7 +5636,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5652,14 +5646,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45162</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5672,7 +5666,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>7.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5715,7 +5709,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5729,10 +5723,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46094</v>
+        <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5745,7 +5739,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>24.5</v>
+        <v>13.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5788,7 +5782,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5802,10 +5796,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45436</v>
+        <v>45588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5817,8 +5811,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5861,7 +5860,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5875,10 +5874,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46108</v>
+        <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5890,13 +5889,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5939,7 +5933,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5953,10 +5947,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46126</v>
+        <v>45596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5969,7 +5963,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>17.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6012,7 +6006,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6026,10 +6020,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46092</v>
+        <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6042,7 +6036,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>37.2</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6085,7 +6079,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6099,10 +6093,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46092</v>
+        <v>45848</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6115,7 +6109,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6158,7 +6152,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6168,14 +6162,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45042</v>
+        <v>45848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6187,13 +6181,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>10.7</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6236,7 +6225,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6246,14 +6235,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45708</v>
+        <v>45546</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6265,13 +6254,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>39.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6314,7 +6298,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6328,10 +6312,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45447</v>
+        <v>45387</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6344,7 +6328,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>15.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6387,7 +6371,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6401,10 +6385,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>45162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6417,7 +6401,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6460,7 +6444,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6474,10 +6458,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>45436</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6490,7 +6474,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6550,7 +6534,7 @@
         <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6606,7 +6590,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6616,14 +6600,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44916</v>
+        <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6636,7 +6620,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6679,7 +6663,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6693,10 +6677,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6709,7 +6693,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>39.8</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6752,7 +6736,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6766,10 +6750,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44721</v>
+        <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6782,7 +6766,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>11.8</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6825,7 +6809,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6835,14 +6819,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44687</v>
+        <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6855,7 +6839,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6898,7 +6882,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6908,14 +6892,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45333</v>
+        <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6928,7 +6912,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6971,7 +6955,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6985,10 +6969,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44795</v>
+        <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7001,7 +6985,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>12.3</v>
+        <v>51.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7044,7 +7028,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7058,10 +7042,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45173</v>
+        <v>45293</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7073,13 +7057,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7122,7 +7101,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7136,10 +7115,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45426</v>
+        <v>46265</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7152,7 +7131,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>62.1</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7195,7 +7174,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7209,10 +7188,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46265</v>
+        <v>46280</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7225,7 +7204,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>54.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7268,7 +7247,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7282,10 +7261,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45387</v>
+        <v>46288</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7298,7 +7277,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7341,7 +7320,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7355,10 +7334,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44916</v>
+        <v>46287</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7371,7 +7350,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7414,7 +7393,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7428,10 +7407,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46280</v>
+        <v>46147</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7444,7 +7423,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>54.2</v>
+        <v>35.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7487,7 +7466,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7501,10 +7480,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46287</v>
+        <v>46202</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7517,7 +7496,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.2</v>
+        <v>10.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7560,7 +7539,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7574,10 +7553,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46147</v>
+        <v>46199</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7590,7 +7569,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>35.7</v>
+        <v>16.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7633,7 +7612,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 29167-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7650,7 +7629,7 @@
         <v>46202</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7663,7 +7642,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10.7</v>
+        <v>2.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7706,7 +7685,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7716,14 +7695,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46202</v>
+        <v>45042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7735,8 +7714,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>2.3</v>
+        <v>10.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7779,7 +7763,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7793,10 +7777,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46199</v>
+        <v>44795</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7809,7 +7793,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>16.9</v>
+        <v>12.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7852,7 +7836,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7862,14 +7846,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46288</v>
+        <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7882,7 +7866,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7925,7 +7909,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7935,14 +7919,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45217</v>
+        <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7954,8 +7938,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7998,7 +7987,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8008,14 +7997,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45848</v>
+        <v>45708</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8027,8 +8016,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8071,7 +8065,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8081,14 +8075,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45848</v>
+        <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8100,8 +8094,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8161,7 +8160,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Späd brosklav
 Blodticka
 Bårdlav
+Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -781,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -797,13 +798,13 @@
         <v>25.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -818,32 +819,37 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="T3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Grantickeporing
 Blanksvart spiklav
+Blågrå svartspik
+Gammelgransskål
 Hornvaxskinn
+Knottrig blåslav
 Kolflarnlav
 Lavskrika
 Luddfingersvamp
 Rödbrun blekspik
 Talltagel
+Tretåig hackspett
 Vaxspindling
 Vedskivlav
+Vitgrynig nållav
 Vitplätt
 Äggvaxskivling
 Luddlav
@@ -891,80 +897,210 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
+          <t>A 32844-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>16</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22</v>
+      </c>
+      <c r="T4" t="n">
+        <v>36</v>
+      </c>
+      <c r="U4" t="n">
+        <v>36</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Tajgaskinn
+Blanksvart spiklav
+Dropptaggsvamp
+Dvärgbägarlav
+Gammelgransskål
+Hornvaxskinn
+Knottrig blåslav
+Kolflarnlav
+Lappmes
+Lavskrika
+Talltagel
+Tretåig hackspett
+Vedflamlav
+Vedskivlav
+Violmussling
+Vitgrynig nållav
+Vitplätt
+Gullgröppa
+Plattlummer
+Skinnlav
+Stuplav
+Timmerticka</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 32844-2026 artfynd.xlsx", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 32844-2026 karta.png", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 32844-2026 georefererad karta.tif", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 32844-2026 FSC-klagomål.docx", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 32844-2026 FSC-klagomål mail.docx", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 32844-2026 tillsynsbegäran.docx", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 32844-2026 tillsynsbegäran mail.docx", "A 32844-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 32844-2026 prioriterade fågelarter.docx", "A 32844-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>A 18726-2024</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D5" s="1" t="n">
         <v>45426</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="E5" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>4.9</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
         <v>11</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>7</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R5" t="n">
         <v>7</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S5" t="n">
         <v>18</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>88</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>17</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Goliatmusseron
@@ -986,158 +1122,36 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 18726-2024 artfynd.xlsx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 18726-2024 karta.png", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 18726-2024 georefererad karta.tif", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 18726-2024 FSC-klagomål.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 18726-2024 FSC-klagomål mail.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 18726-2024 tillsynsbegäran.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 18726-2024 tillsynsbegäran mail.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 18726-2024 prioriterade fågelarter.docx", "A 18726-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 32844-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>10</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>14</v>
-      </c>
-      <c r="T5" t="n">
-        <v>19</v>
-      </c>
-      <c r="U5" t="n">
-        <v>19</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Hornvaxskinn
-Knottrig blåslav
-Lappmes
-Lavskrika
-Talltagel
-Tretåig hackspett
-Vedskivlav
-Violmussling
-Vitplätt
-Plattlummer
-Skinnlav
-Stuplav
-Timmerticka</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 32844-2026 artfynd.xlsx", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 32844-2026 karta.png", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 32844-2026 georefererad karta.tif", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 32844-2026 FSC-klagomål.docx", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 32844-2026 FSC-klagomål mail.docx", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 32844-2026 tillsynsbegäran.docx", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 32844-2026 tillsynsbegäran mail.docx", "A 32844-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 32844-2026 prioriterade fågelarter.docx", "A 32844-2026")</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1280,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1403,7 +1417,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1517,7 +1531,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1613,7 +1627,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20570-2025</t>
+          <t>A 29171-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1627,10 +1641,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45775</v>
+        <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,22 +1656,17 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>31.4</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -1672,21 +1681,247 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Knottrig blåslav
+Talltagel
+Tallticka
+Vitplätt
+Hultbräken
+Ormbär</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29171-2026 artfynd.xlsx", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29171-2026 karta.png", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29171-2026 georefererad karta.tif", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29171-2026 FSC-klagomål.docx", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29171-2026 FSC-klagomål mail.docx", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29171-2026 tillsynsbegäran.docx", "A 29171-2026")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29171-2026 tillsynsbegäran mail.docx", "A 29171-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29167-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav
+Gammelgransskål
+Reliktbock
+Talltagel
+Tallticka
+Vedskivlav</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29167-2026 artfynd.xlsx", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29167-2026 karta.png", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29167-2026 georefererad karta.tif", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29167-2026 FSC-klagomål.docx", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29167-2026 FSC-klagomål mail.docx", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29167-2026 tillsynsbegäran.docx", "A 29167-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29167-2026 tillsynsbegäran mail.docx", "A 29167-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A 20570-2025</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45775</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>7</v>
       </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -1695,107 +1930,107 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20570-2025 artfynd.xlsx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20570-2025 karta.png", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20570-2025 georefererad karta.tif", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20570-2025 FSC-klagomål.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20570-2025 FSC-klagomål mail.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20570-2025 tillsynsbegäran.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20570-2025 tillsynsbegäran mail.docx", "A 20570-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 24485-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46170</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>14.8</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>4</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>5</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Dropptaggsvamp
@@ -1803,1242 +2038,1024 @@
 Plattlummer</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 24485-2026 artfynd.xlsx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 24485-2026 karta.png", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 24485-2026 georefererad karta.tif", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 24485-2026 FSC-klagomål.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 24485-2026 FSC-klagomål mail.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 24485-2026 tillsynsbegäran.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 24485-2026 tillsynsbegäran mail.docx", "A 24485-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 29171-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46202</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>4</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Vitplätt
-Hultbräken
-Ormbär</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29171-2026 artfynd.xlsx", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29171-2026 karta.png", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29171-2026 georefererad karta.tif", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29171-2026 FSC-klagomål.docx", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29171-2026 FSC-klagomål mail.docx", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29171-2026 tillsynsbegäran.docx", "A 29171-2026")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29171-2026 tillsynsbegäran mail.docx", "A 29171-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J13" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 22495-2024</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>45447</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>7.1</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S15" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tajgafältmätare
 Blåhake
 Lavskrika</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 21183-2025</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D16" s="1" t="n">
         <v>45779</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>31.9</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>3</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lappmes
 Venhavre
 Kärrtrumpetmossa</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>A 53309-2023</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D17" s="1" t="n">
         <v>45229</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>1.6</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>A 20780-2025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D18" s="1" t="n">
         <v>45776</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="E18" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>5.7</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lappranunkel
 Stuplav</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 17740-2023</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45035</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>20.1</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>100.3</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>A 58860-2022</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D21" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E21" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0.3</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>2</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D21" s="1" t="n">
+      <c r="D22" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
+      <c r="E22" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>100.3</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>2</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 45810-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44844</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46291</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 45810-2022 artfynd.xlsx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 45810-2022 karta.png", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 45810-2022 georefererad karta.tif", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 45810-2022 FSC-klagomål.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 45810-2022 FSC-klagomål mail.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 45810-2022 tillsynsbegäran.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 45810-2022 tillsynsbegäran mail.docx", "A 45810-2022")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 45810-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3048,14 +3065,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45645</v>
+        <v>44844</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3067,8 +3084,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3101,53 +3123,49 @@
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 45810-2022 artfynd.xlsx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 45810-2022 karta.png", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 45810-2022 georefererad karta.tif", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 45810-2022 FSC-klagomål.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 45810-2022 FSC-klagomål mail.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 45810-2022 tillsynsbegäran.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 45810-2022 tillsynsbegäran mail.docx", "A 45810-2022")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3161,10 +3179,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45258</v>
+        <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3177,7 +3195,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>19.8</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
@@ -3210,10 +3228,10 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
@@ -3221,42 +3239,42 @@
         </is>
       </c>
       <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3270,10 +3288,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46037</v>
+        <v>45258</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3286,16 +3304,16 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>19.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3310,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3319,49 +3337,53 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE25">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3371,14 +3393,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44958</v>
+        <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3391,7 +3413,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3400,10 +3422,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -3418,7 +3440,7 @@
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3431,42 +3453,42 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3476,14 +3498,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45326</v>
+        <v>44958</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3496,7 +3518,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.5</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3505,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3523,7 +3545,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3532,46 +3554,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3585,10 +3607,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45405</v>
+        <v>45326</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3601,7 +3623,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3641,42 +3663,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3690,10 +3712,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46265</v>
+        <v>45405</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3706,7 +3728,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3742,46 +3764,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 45205-2022</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3791,14 +3813,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44840</v>
+        <v>46265</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3810,13 +3832,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3825,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3840,26 +3857,58 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53752-2022</t>
+          <t>A 45205-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3869,14 +3918,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44875</v>
+        <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3890,11 +3939,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3937,7 +3986,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 53752-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3951,10 +4000,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3966,8 +4015,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4010,7 +4064,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4027,7 +4081,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4040,7 +4094,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4083,7 +4137,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4097,10 +4151,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45361</v>
+        <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4113,7 +4167,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4156,7 +4210,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4170,10 +4224,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45331</v>
+        <v>45361</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4186,7 +4240,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.9</v>
+        <v>8.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4229,7 +4283,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4243,10 +4297,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46024</v>
+        <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4259,7 +4313,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10.2</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4302,7 +4356,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4316,10 +4370,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45447</v>
+        <v>46024</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4332,7 +4386,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4375,7 +4429,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4389,10 +4443,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45217</v>
+        <v>45447</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4405,7 +4459,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4448,7 +4502,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4462,10 +4516,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44979</v>
+        <v>45217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4477,13 +4531,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4526,7 +4575,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4540,10 +4589,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46037</v>
+        <v>44979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4555,8 +4604,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>31.3</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4599,7 +4653,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4613,10 +4667,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44916</v>
+        <v>46037</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4629,7 +4683,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>31.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4672,7 +4726,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4686,10 +4740,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45447</v>
+        <v>44916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4702,7 +4756,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>15.6</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4745,7 +4799,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4759,10 +4813,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45333</v>
+        <v>45447</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4775,7 +4829,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>15.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4818,7 +4872,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4832,10 +4886,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46094</v>
+        <v>45333</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4848,7 +4902,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>24.5</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4891,7 +4945,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4905,10 +4959,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45944</v>
+        <v>46094</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4920,13 +4974,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>22.6</v>
+        <v>24.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4969,7 +5018,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4983,10 +5032,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45426</v>
+        <v>45944</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4998,8 +5047,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>62.1</v>
+        <v>22.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5042,7 +5096,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5052,14 +5106,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46108</v>
+        <v>45426</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5071,13 +5125,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.7</v>
+        <v>62.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5120,7 +5169,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5130,14 +5179,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>46108</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5149,8 +5198,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>20.1</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5193,7 +5247,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5207,10 +5261,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5223,7 +5277,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>27.3</v>
+        <v>20.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5266,7 +5320,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5280,10 +5334,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44979</v>
+        <v>45776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5295,13 +5349,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.6</v>
+        <v>27.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5344,7 +5393,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5358,10 +5407,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46126</v>
+        <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5373,8 +5422,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5417,7 +5471,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5431,10 +5485,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46092</v>
+        <v>46126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5447,7 +5501,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>37.2</v>
+        <v>5.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5490,7 +5544,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5507,7 +5561,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5520,7 +5574,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>37.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5563,7 +5617,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5577,10 +5631,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44721</v>
+        <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5593,7 +5647,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.8</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5636,7 +5690,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5650,10 +5704,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>44721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5666,7 +5720,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5709,7 +5763,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5726,7 +5780,7 @@
         <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5739,7 +5793,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>13.4</v>
+        <v>7.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5782,7 +5836,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5796,10 +5850,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45588</v>
+        <v>44916</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5811,13 +5865,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>13.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5860,7 +5909,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5870,14 +5919,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44805</v>
+        <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5889,8 +5938,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5933,7 +5987,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5943,14 +5997,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45596</v>
+        <v>44805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5963,7 +6017,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.4</v>
+        <v>3.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6006,7 +6060,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6020,10 +6074,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6036,7 +6090,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>17.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6079,7 +6133,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6093,10 +6147,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45848</v>
+        <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6109,7 +6163,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6152,7 +6206,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6169,7 +6223,7 @@
         <v>45848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6182,7 +6236,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6225,7 +6279,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6239,10 +6293,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45546</v>
+        <v>45848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6255,7 +6309,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>39.8</v>
+        <v>5.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6298,7 +6352,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6312,10 +6366,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45387</v>
+        <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6328,7 +6382,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>8.199999999999999</v>
+        <v>39.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6371,7 +6425,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6385,10 +6439,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45162</v>
+        <v>45387</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6401,7 +6455,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>11.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6444,7 +6498,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6458,10 +6512,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45436</v>
+        <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6474,7 +6528,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6517,7 +6571,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6531,10 +6585,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46210</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6547,7 +6601,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6590,7 +6644,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6600,14 +6654,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44687</v>
+        <v>46210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6620,7 +6674,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6663,7 +6717,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6673,14 +6727,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46210</v>
+        <v>44687</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6693,7 +6747,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6736,7 +6790,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6753,7 +6807,7 @@
         <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6766,7 +6820,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6809,7 +6863,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6823,10 +6877,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44748</v>
+        <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6839,7 +6893,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>15.2</v>
+        <v>2.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6882,7 +6936,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6892,14 +6946,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45162</v>
+        <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6912,7 +6966,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>15.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6955,7 +7009,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6965,14 +7019,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
         <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6985,7 +7039,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>51.9</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7028,7 +7082,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7038,14 +7092,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45293</v>
+        <v>45162</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7058,7 +7112,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>51.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7101,7 +7155,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7111,14 +7165,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46265</v>
+        <v>45293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7131,7 +7185,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7174,7 +7228,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7188,10 +7242,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46280</v>
+        <v>46265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7204,7 +7258,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>54.2</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7247,7 +7301,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7261,10 +7315,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46288</v>
+        <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7277,7 +7331,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>13.6</v>
+        <v>54.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7320,7 +7374,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7334,10 +7388,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7350,7 +7404,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7393,7 +7447,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7407,10 +7461,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46147</v>
+        <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7423,7 +7477,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>35.7</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7466,7 +7520,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7480,10 +7534,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46202</v>
+        <v>46147</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7496,7 +7550,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>10.7</v>
+        <v>35.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7539,7 +7593,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 29231-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7553,10 +7607,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7569,7 +7623,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>16.9</v>
+        <v>10.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7612,7 +7666,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29167-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7626,10 +7680,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7642,7 +7696,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.3</v>
+        <v>16.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7702,7 +7756,7 @@
         <v>45042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7780,7 +7834,7 @@
         <v>44795</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7853,7 +7907,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7926,7 +7980,7 @@
         <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8004,7 +8058,7 @@
         <v>45708</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8082,7 +8136,7 @@
         <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8160,7 +8214,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>46000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
         <v>46202</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>45775</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>46170</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>45281</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2194,7 +2194,7 @@
         <v>45447</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>45779</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>45229</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>45776</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45035</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>45222</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44844</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45258</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44958</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>45326</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>45405</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>46265</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>44875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>44623</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>44623</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45361</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45331</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>46024</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45447</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>45217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>46037</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>45447</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>45333</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46094</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>45944</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45426</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>46108</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>45777</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45776</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>44979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>46126</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46092</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>44721</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>44916</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>45588</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         <v>44805</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>45848</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45848</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45387</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>46210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44687</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>46210</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>44748</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         <v>45162</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>45293</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46265</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>46288</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>46147</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         <v>46202</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>46199</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>45042</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44795</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45334</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>45236</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45708</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>45173</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>45714</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AE90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30524-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46210</v>
+        <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,19 +1430,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1454,21 +1454,139 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Knottrig blåslav
+Lappmes
+Lavskrika
+Reliktbock
+Sotvaxskivling
+Talltagel
+Vedskivlav
+Vitgrynig nållav
+Nordtätskinn</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 30524-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>22</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>22</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Mörk blåslav
 Blanksvart spiklav
@@ -1482,107 +1600,107 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>A 61178-2025</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D10" s="1" t="n">
         <v>46000</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
+      <c r="E10" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>31.3</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
         <v>7</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>8</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>9</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>10</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Skrovlig taggsvamp
 Blanksvart spiklav
@@ -1595,107 +1713,224 @@
 Plattlummer</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61178-2025 artfynd.xlsx", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61178-2025 karta.png", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61178-2025 georefererad karta.tif", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61178-2025 FSC-klagomål.docx", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61178-2025 FSC-klagomål mail.docx", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61178-2025 tillsynsbegäran.docx", "A 61178-2025")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61178-2025 tillsynsbegäran mail.docx", "A 61178-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 29231-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="n">
+        <v>11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>11</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Blanksvart spiklav
+Blågrå svartspik
+Gammelgransskål
+Knottrig blåslav
+Lavskrika
+Tallriska
+Vedskivlav
+Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="W11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29231-2026 artfynd.xlsx", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="X11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29231-2026 karta.png", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="Y11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29231-2026 georefererad karta.tif", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="AA11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29231-2026 FSC-klagomål.docx", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="AB11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29231-2026 FSC-klagomål mail.docx", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="AC11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29231-2026 tillsynsbegäran.docx", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="AD11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29231-2026 tillsynsbegäran mail.docx", "A 29231-2026")</f>
+        <v/>
+      </c>
+      <c r="AE11">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29231-2026 prioriterade fågelarter.docx", "A 29231-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>A 29171-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
+      <c r="E12" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>4.9</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
         <v>4</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S12" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T12" t="n">
         <v>8</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U12" t="n">
         <v>8</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knottrig blåslav
@@ -1706,107 +1941,107 @@
 Ormbär</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29171-2026 artfynd.xlsx", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29171-2026 karta.png", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29171-2026 georefererad karta.tif", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29171-2026 FSC-klagomål.docx", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29171-2026 FSC-klagomål mail.docx", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29171-2026 tillsynsbegäran.docx", "A 29171-2026")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD12">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29171-2026 tillsynsbegäran mail.docx", "A 29171-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>A 29167-2026</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D13" s="1" t="n">
         <v>46202</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
+      <c r="E13" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>2.3</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>6</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>6</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>7</v>
       </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Blanksvart spiklav
 Gammelgransskål
@@ -1816,112 +2051,112 @@
 Vedskivlav</t>
         </is>
       </c>
-      <c r="W11">
+      <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29167-2026 artfynd.xlsx", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="X11">
+      <c r="X13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29167-2026 karta.png", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="Y11">
+      <c r="Y13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29167-2026 georefererad karta.tif", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="AA11">
+      <c r="AA13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29167-2026 FSC-klagomål.docx", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="AB11">
+      <c r="AB13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29167-2026 FSC-klagomål mail.docx", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="AC11">
+      <c r="AC13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29167-2026 tillsynsbegäran.docx", "A 29167-2026")</f>
         <v/>
       </c>
-      <c r="AD11">
+      <c r="AD13">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29167-2026 tillsynsbegäran mail.docx", "A 29167-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>A 20570-2025</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
+      <c r="D14" s="1" t="n">
         <v>45775</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="E14" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I12" t="n">
+      <c r="I14" t="n">
         <v>31.4</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S14" t="n">
         <v>5</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T14" t="n">
         <v>7</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Harticka
@@ -1930,107 +2165,107 @@
 Stuplav</t>
         </is>
       </c>
-      <c r="W12">
+      <c r="W14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20570-2025 artfynd.xlsx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="X12">
+      <c r="X14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20570-2025 karta.png", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="Y12">
+      <c r="Y14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20570-2025 georefererad karta.tif", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AA12">
+      <c r="AA14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20570-2025 FSC-klagomål.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AB12">
+      <c r="AB14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20570-2025 FSC-klagomål mail.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AC12">
+      <c r="AC14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20570-2025 tillsynsbegäran.docx", "A 20570-2025")</f>
         <v/>
       </c>
-      <c r="AD12">
+      <c r="AD14">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20570-2025 tillsynsbegäran mail.docx", "A 20570-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>A 24485-2026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D15" s="1" t="n">
         <v>46170</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
+      <c r="E15" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>14.8</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>3</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S15" t="n">
         <v>4</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T15" t="n">
         <v>5</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Dropptaggsvamp
@@ -2038,1243 +2273,1024 @@
 Plattlummer</t>
         </is>
       </c>
-      <c r="W13">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 24485-2026 artfynd.xlsx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="X13">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 24485-2026 karta.png", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="Y13">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 24485-2026 georefererad karta.tif", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AA13">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 24485-2026 FSC-klagomål.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AB13">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 24485-2026 FSC-klagomål mail.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AC13">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 24485-2026 tillsynsbegäran.docx", "A 24485-2026")</f>
         <v/>
       </c>
-      <c r="AD13">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 24485-2026 tillsynsbegäran mail.docx", "A 24485-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 64829-2023</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för annat ändamål</t>
         </is>
       </c>
-      <c r="D14" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45281</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
+      <c r="E19" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>31.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T19" t="n">
         <v>3</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 20780-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J15" t="n">
+      <c r="D20" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>3</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 20780-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45776</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lappranunkel
 Stuplav</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 17740-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45035</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I24" t="n">
         <v>20.1</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 45810-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44844</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 45810-2022 artfynd.xlsx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 45810-2022 karta.png", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 45810-2022 georefererad karta.tif", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 45810-2022 FSC-klagomål.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 45810-2022 FSC-klagomål mail.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 45810-2022 tillsynsbegäran.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 45810-2022 tillsynsbegäran mail.docx", "A 45810-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 61066-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45645</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 45810-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3284,14 +3300,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45258</v>
+        <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3303,8 +3319,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>19.8</v>
+        <v>6.8</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3337,53 +3358,49 @@
         <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 45810-2022 artfynd.xlsx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 45810-2022 karta.png", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 45810-2022 georefererad karta.tif", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 45810-2022 FSC-klagomål.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 45810-2022 FSC-klagomål mail.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 45810-2022 tillsynsbegäran.docx", "A 45810-2022")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 45810-2022 tillsynsbegäran mail.docx", "A 45810-2022")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3397,10 +3414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46037</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3413,16 +3430,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3437,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3449,46 +3466,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3498,14 +3519,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44958</v>
+        <v>45258</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3518,10 +3539,10 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>19.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -3530,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3542,51 +3563,55 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3610,7 +3635,7 @@
         <v>45326</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3723,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3712,10 +3737,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45405</v>
+        <v>46037</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3728,7 +3753,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3764,46 +3789,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3817,10 +3842,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46265</v>
+        <v>45405</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3833,7 +3858,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3869,46 +3894,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 45205-2022</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3922,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44840</v>
+        <v>44958</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3937,13 +3962,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3955,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3967,26 +3987,58 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Fjällsotlav</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 53752-2022</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4000,10 +4052,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44875</v>
+        <v>46265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4015,13 +4067,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4030,7 +4077,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4045,26 +4092,58 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 10546-2022</t>
+          <t>A 45205-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4074,14 +4153,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44623</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4093,8 +4172,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4137,7 +4221,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10545-2022</t>
+          <t>A 53752-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4151,10 +4235,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44623</v>
+        <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4166,8 +4250,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4210,7 +4299,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 10546-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4224,10 +4313,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45361</v>
+        <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4240,7 +4329,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>8.4</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4283,7 +4372,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 10545-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4297,10 +4386,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45331</v>
+        <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4313,7 +4402,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4356,7 +4445,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4370,10 +4459,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46024</v>
+        <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4386,7 +4475,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10.2</v>
+        <v>11.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4429,7 +4518,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4443,10 +4532,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45447</v>
+        <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4459,7 +4548,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>17.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4502,7 +4591,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4516,10 +4605,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45217</v>
+        <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4532,7 +4621,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.3</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4575,7 +4664,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4589,10 +4678,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44979</v>
+        <v>45217</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4604,13 +4693,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4653,7 +4737,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4667,10 +4751,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46037</v>
+        <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4683,7 +4767,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31.3</v>
+        <v>13.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4726,7 +4810,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4736,14 +4820,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44916</v>
+        <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4756,7 +4840,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4799,7 +4883,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4813,10 +4897,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45447</v>
+        <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4828,8 +4912,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>15.6</v>
+        <v>22.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4872,7 +4961,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4886,10 +4975,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45333</v>
+        <v>45848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4902,7 +4991,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4945,7 +5034,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4959,10 +5048,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46094</v>
+        <v>45848</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4975,7 +5064,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>24.5</v>
+        <v>8.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5018,7 +5107,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5032,10 +5121,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45944</v>
+        <v>46024</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5047,13 +5136,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>22.6</v>
+        <v>10.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5096,7 +5180,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5110,10 +5194,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45426</v>
+        <v>45776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5126,7 +5210,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>62.1</v>
+        <v>27.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5169,7 +5253,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5179,14 +5263,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46108</v>
+        <v>45777</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5198,13 +5282,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>20.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5247,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5261,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45777</v>
+        <v>46037</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5277,7 +5356,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>20.1</v>
+        <v>31.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5320,7 +5399,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5330,14 +5409,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45776</v>
+        <v>45334</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5350,7 +5429,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>27.3</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5393,7 +5472,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5407,10 +5486,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44979</v>
+        <v>45361</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5422,13 +5501,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5471,7 +5545,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5485,10 +5559,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46126</v>
+        <v>45331</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5501,7 +5575,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5544,7 +5618,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5558,10 +5632,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46092</v>
+        <v>44748</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5574,7 +5648,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>37.2</v>
+        <v>15.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5617,7 +5691,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5631,10 +5705,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46092</v>
+        <v>44979</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5646,8 +5720,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5690,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5700,14 +5779,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44721</v>
+        <v>45293</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5720,7 +5799,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5763,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5777,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44916</v>
+        <v>45162</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5793,7 +5872,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7.2</v>
+        <v>51.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5836,7 +5915,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5850,10 +5929,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44916</v>
+        <v>46094</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5866,7 +5945,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>13.4</v>
+        <v>24.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5909,7 +5988,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5919,14 +5998,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45588</v>
+        <v>45236</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5940,11 +6019,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5987,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6001,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44805</v>
+        <v>46108</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6016,8 +6095,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6060,7 +6144,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6074,10 +6158,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45596</v>
+        <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6090,7 +6174,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.4</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6133,7 +6217,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6147,10 +6231,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45447</v>
+        <v>46126</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6163,7 +6247,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6206,7 +6290,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6220,10 +6304,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45848</v>
+        <v>46092</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6236,7 +6320,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8.4</v>
+        <v>37.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6279,7 +6363,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6293,10 +6377,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45848</v>
+        <v>46092</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6309,7 +6393,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6352,7 +6436,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6366,10 +6450,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45546</v>
+        <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6381,8 +6465,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>39.8</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6425,7 +6514,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6439,10 +6528,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45387</v>
+        <v>44979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6454,8 +6543,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6498,7 +6592,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6508,14 +6602,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
         <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6528,7 +6622,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11.7</v>
+        <v>1.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6588,7 +6682,7 @@
         <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6644,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6654,14 +6748,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46210</v>
+        <v>45042</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6673,8 +6767,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>6.8</v>
+        <v>10.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6717,7 +6816,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6731,10 +6830,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44687</v>
+        <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6746,8 +6845,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6790,7 +6894,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6804,10 +6908,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46210</v>
+        <v>45447</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6820,7 +6924,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>5</v>
+        <v>15.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6863,7 +6967,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6877,10 +6981,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46210</v>
+        <v>44916</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6893,7 +6997,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6936,7 +7040,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6950,10 +7054,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44748</v>
+        <v>46210</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6966,7 +7070,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>15.2</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7009,7 +7113,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7019,14 +7123,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45162</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7039,7 +7143,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7082,7 +7186,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7096,10 +7200,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45162</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7112,7 +7216,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>51.9</v>
+        <v>6.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7155,7 +7259,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7165,14 +7269,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45293</v>
+        <v>45546</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7185,7 +7289,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.8</v>
+        <v>39.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7228,7 +7332,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7242,10 +7346,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46265</v>
+        <v>44721</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7258,7 +7362,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2.7</v>
+        <v>11.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7301,7 +7405,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7311,14 +7415,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46280</v>
+        <v>44687</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7331,7 +7435,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>54.2</v>
+        <v>1.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7374,7 +7478,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7388,10 +7492,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46288</v>
+        <v>45333</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7404,7 +7508,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>13.6</v>
+        <v>1.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7447,7 +7551,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7461,10 +7565,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46287</v>
+        <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7477,7 +7581,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>12.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7520,7 +7624,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7530,14 +7634,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46147</v>
+        <v>45173</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7549,8 +7653,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>35.7</v>
+        <v>1.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7593,7 +7702,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 29231-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7607,10 +7716,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46202</v>
+        <v>45426</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7623,7 +7732,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>10.7</v>
+        <v>62.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7666,7 +7775,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7680,10 +7789,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46199</v>
+        <v>45387</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7696,7 +7805,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>16.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7739,7 +7848,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7749,14 +7858,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45042</v>
+        <v>44916</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7768,13 +7877,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>10.7</v>
+        <v>3.2</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7817,7 +7921,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7831,10 +7935,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44795</v>
+        <v>46265</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7847,7 +7951,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>12.3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7890,7 +7994,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7900,14 +8004,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45334</v>
+        <v>46287</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7920,7 +8024,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7963,7 +8067,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7973,14 +8077,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45236</v>
+        <v>46147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7992,13 +8096,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>35.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8041,7 +8140,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8051,14 +8150,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45708</v>
+        <v>46288</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8070,13 +8169,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>0.8</v>
+        <v>13.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8119,7 +8213,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8129,14 +8223,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45173</v>
+        <v>46293</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8148,13 +8242,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8194,78 +8283,151 @@
       </c>
       <c r="V88" s="2" t="inlineStr"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
+          <t>A 37993-2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>S 637-2025</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D89" s="1" t="n">
+      <c r="D90" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="E89" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
+      <c r="E90" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
         <v>49.3</v>
       </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="2" t="inlineStr"/>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 30524-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,45 +1430,159 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.9</v>
+        <v>21.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Mörk blåslav
+Blanksvart spiklav
+Blågrå svartspik
+Gammelgransskål
+Knottrig blåslav
+Kolflarnlav
+Ladlav
+Vedskivlav
+Äggvaxskivling
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 29048-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Knottrig blåslav
@@ -1482,150 +1596,36 @@
 Nordtätskinn</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 30524-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Mörk blåslav
-Blanksvart spiklav
-Blågrå svartspik
-Gammelgransskål
-Knottrig blåslav
-Kolflarnlav
-Ladlav
-Vedskivlav
-Äggvaxskivling
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2371,374 +2371,374 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 17740-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44896</v>
+        <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,23 +2886,28 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>20.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2914,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2923,367 +2928,362 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>100.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45258</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45326</v>
+        <v>46037</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.5</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3684,46 +3684,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46037</v>
+        <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3762,10 +3762,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3793,42 +3793,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45405</v>
+        <v>45326</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>7.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3898,42 +3898,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3943,14 +3943,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44958</v>
+        <v>45405</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3972,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -3999,39 +3999,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>46265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45162</v>
+        <v>45361</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45596</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>17.4</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45447</v>
+        <v>46024</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45217</v>
+        <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4737,7 +4737,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44916</v>
+        <v>45217</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>13.4</v>
+        <v>1.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4820,14 +4820,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44805</v>
+        <v>44979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4839,8 +4839,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4883,7 +4888,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4897,10 +4902,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45944</v>
+        <v>44916</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4912,13 +4917,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>22.6</v>
+        <v>3.2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4961,7 +4961,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45848</v>
+        <v>46037</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>31.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45848</v>
+        <v>45447</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8.4</v>
+        <v>15.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46024</v>
+        <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10.2</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45776</v>
+        <v>45848</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>27.3</v>
+        <v>8.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5253,7 +5253,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5267,10 +5267,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45777</v>
+        <v>45848</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20.1</v>
+        <v>5.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5340,10 +5340,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46037</v>
+        <v>45944</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,8 +5355,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>31.3</v>
+        <v>22.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5399,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5409,14 +5414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45334</v>
+        <v>45426</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5429,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>62.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5472,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5486,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45361</v>
+        <v>45777</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5502,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>20.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5545,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5559,10 +5564,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45331</v>
+        <v>45776</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5575,7 +5580,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>27.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5618,7 +5623,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5632,10 +5637,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44748</v>
+        <v>44979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5647,8 +5652,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>15.2</v>
+        <v>4.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5691,7 +5701,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5705,10 +5715,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44979</v>
+        <v>44721</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5720,13 +5730,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>4.6</v>
+        <v>11.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5774,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5779,14 +5784,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45293</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5804,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5847,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5861,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45162</v>
+        <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5872,7 +5877,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>51.9</v>
+        <v>13.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5915,7 +5920,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5929,10 +5934,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46094</v>
+        <v>45588</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5944,8 +5949,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>24.5</v>
+        <v>3.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5988,7 +5998,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6002,10 +6012,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45236</v>
+        <v>44805</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6017,13 +6027,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6071,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6076,14 +6081,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46108</v>
+        <v>45596</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6095,13 +6100,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>17.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6161,7 +6161,7 @@
         <v>45447</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6217,7 +6217,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6231,10 +6231,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46126</v>
+        <v>46094</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>24.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6290,7 +6290,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6300,14 +6300,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46092</v>
+        <v>46108</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6319,8 +6319,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>37.2</v>
+        <v>1.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6363,7 +6368,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6377,10 +6382,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46092</v>
+        <v>46126</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6393,7 +6398,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6436,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6450,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45588</v>
+        <v>46092</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6465,13 +6470,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>3.7</v>
+        <v>37.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6514,7 +6514,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6528,10 +6528,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44979</v>
+        <v>46092</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6543,13 +6543,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6592,7 +6587,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6602,14 +6597,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45162</v>
+        <v>45546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6622,7 +6617,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.6</v>
+        <v>39.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6665,7 +6660,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6679,10 +6674,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>45387</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6695,7 +6690,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6738,7 +6733,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6748,14 +6743,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45042</v>
+        <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,13 +6762,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>10.7</v>
+        <v>11.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6816,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6826,14 +6816,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45708</v>
+        <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6845,13 +6835,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6894,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6904,14 +6889,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45447</v>
+        <v>44687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6924,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>15.6</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6967,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6981,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44916</v>
+        <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6997,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.2</v>
+        <v>15.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7040,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7050,14 +7035,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46210</v>
+        <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7070,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7113,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7127,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>45162</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7143,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>51.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7186,7 +7171,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7196,14 +7181,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>45293</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7216,7 +7201,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6.8</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7259,7 +7244,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7273,10 +7258,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7289,7 +7274,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>39.8</v>
+        <v>6.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7332,7 +7317,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7346,10 +7331,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44721</v>
+        <v>46210</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7362,7 +7347,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11.8</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7405,7 +7390,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7415,14 +7400,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44687</v>
+        <v>46210</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7435,7 +7420,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7478,7 +7463,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7488,14 +7473,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45333</v>
+        <v>45042</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7507,8 +7492,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>1.8</v>
+        <v>10.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7568,7 +7558,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7624,7 +7614,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7638,10 +7628,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45173</v>
+        <v>45334</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7653,13 +7643,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7702,7 +7687,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7712,14 +7697,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45426</v>
+        <v>45236</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7731,8 +7716,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>62.1</v>
+        <v>6.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7775,7 +7765,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7785,14 +7775,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45387</v>
+        <v>45708</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7804,8 +7794,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>8.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7848,7 +7843,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7862,10 +7857,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44916</v>
+        <v>46265</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7878,7 +7873,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7921,7 +7916,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7931,14 +7926,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46265</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7950,8 +7945,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7994,7 +7994,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         <v>46147</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>13.6</v>
+        <v>9.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8303,7 +8303,7 @@
         <v>46280</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30524-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46210</v>
+        <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,19 +1430,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1454,21 +1454,139 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Knottrig blåslav
+Lappmes
+Lavskrika
+Reliktbock
+Sotvaxskivling
+Talltagel
+Vedskivlav
+Vitgrynig nållav
+Nordtätskinn</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 30524-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>22</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>22</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Mörk blåslav
 Blanksvart spiklav
@@ -1482,150 +1600,32 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 29048-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Knottrig blåslav
-Lappmes
-Lavskrika
-Reliktbock
-Sotvaxskivling
-Talltagel
-Vedskivlav
-Vitgrynig nållav
-Nordtätskinn</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2371,493 +2371,493 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 20780-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 22495-2024</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45447</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>7.1</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>2</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Tajgafältmätare
 Blåhake
 Lavskrika</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
         <v/>
       </c>
-      <c r="AE17">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 20780-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45776</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17740-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45035</v>
+        <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,28 +2886,23 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>20.1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2919,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2928,336 +2923,341 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>100.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
       <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
@@ -3307,7 +3307,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45258</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46037</v>
+        <v>45405</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3684,39 +3684,39 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45326</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45405</v>
+        <v>46037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3999,39 +3999,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>46265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45361</v>
+        <v>44721</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.4</v>
+        <v>11.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>44687</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46024</v>
+        <v>44979</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4620,8 +4620,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4664,7 +4669,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4678,10 +4683,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45447</v>
+        <v>45333</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4694,7 +4699,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4737,7 +4742,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4751,10 +4756,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45217</v>
+        <v>44795</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4767,7 +4772,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4810,7 +4815,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4820,14 +4825,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44979</v>
+        <v>45162</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4839,13 +4844,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44916</v>
+        <v>45334</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4961,7 +4961,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46037</v>
+        <v>45361</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>31.3</v>
+        <v>8.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45447</v>
+        <v>45331</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>15.6</v>
+        <v>3.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45333</v>
+        <v>44748</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>15.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45848</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5209,8 +5209,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5253,7 +5258,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5263,14 +5268,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45848</v>
+        <v>45293</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5283,7 +5288,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.1</v>
+        <v>0.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5331,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5336,14 +5341,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45944</v>
+        <v>45173</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5361,7 +5366,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>22.6</v>
+        <v>1.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5421,7 +5426,7 @@
         <v>45426</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5477,7 +5482,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5496,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45777</v>
+        <v>45436</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5507,7 +5512,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>20.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5550,7 +5555,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5569,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45776</v>
+        <v>45162</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5580,7 +5585,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>27.3</v>
+        <v>11.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5628,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5637,10 +5642,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44979</v>
+        <v>45387</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5652,13 +5657,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44721</v>
+        <v>44916</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>11.8</v>
+        <v>3.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>45162</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.2</v>
+        <v>51.9</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5857,14 +5857,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44916</v>
+        <v>45042</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5876,8 +5876,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>13.4</v>
+        <v>10.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5920,7 +5925,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5930,14 +5935,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45588</v>
+        <v>45236</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5951,11 +5956,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5998,7 +6003,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6008,14 +6013,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44805</v>
+        <v>44916</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6028,7 +6033,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.1</v>
+        <v>13.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6071,7 +6076,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6085,10 +6090,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45596</v>
+        <v>45447</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6101,7 +6106,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17.4</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6144,7 +6149,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6158,10 +6163,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45447</v>
+        <v>45217</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6174,7 +6179,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6217,7 +6222,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6227,14 +6232,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46094</v>
+        <v>44805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6247,7 +6252,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>24.5</v>
+        <v>3.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6290,7 +6295,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6304,10 +6309,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46108</v>
+        <v>45708</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6325,7 +6330,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6368,7 +6373,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6382,10 +6387,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46126</v>
+        <v>45447</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6398,7 +6403,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5.2</v>
+        <v>15.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6441,7 +6446,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6455,10 +6460,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46092</v>
+        <v>44916</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6471,7 +6476,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>37.2</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6514,7 +6519,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6528,10 +6533,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46092</v>
+        <v>45546</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6544,7 +6549,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>39.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6587,7 +6592,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6601,10 +6606,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45546</v>
+        <v>45848</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6617,7 +6622,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>39.8</v>
+        <v>5.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6660,7 +6665,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6674,10 +6679,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45387</v>
+        <v>45848</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6690,7 +6695,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6752,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45162</v>
+        <v>45588</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,8 +6767,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>11.7</v>
+        <v>3.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6806,7 +6816,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,10 +6830,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45436</v>
+        <v>45944</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,8 +6845,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>9.699999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6879,7 +6894,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6889,14 +6904,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44687</v>
+        <v>45776</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6924,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>27.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6967,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6966,10 +6981,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44748</v>
+        <v>45777</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6982,7 +6997,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>15.2</v>
+        <v>20.1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7040,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7035,14 +7050,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45162</v>
+        <v>45596</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7055,7 +7070,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>17.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7113,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7127,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45162</v>
+        <v>45447</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7143,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>51.9</v>
+        <v>9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7171,7 +7186,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7181,14 +7196,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45293</v>
+        <v>46024</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7201,7 +7216,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>10.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7244,7 +7259,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,10 +7273,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>46037</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7274,7 +7289,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.8</v>
+        <v>31.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7332,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7346,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46210</v>
+        <v>46094</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7347,7 +7362,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>5</v>
+        <v>24.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7390,7 +7405,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7400,14 +7415,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46210</v>
+        <v>46108</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7419,8 +7434,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7463,7 +7483,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7473,14 +7493,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45042</v>
+        <v>46126</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7492,13 +7512,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>10.7</v>
+        <v>5.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7541,7 +7556,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7555,10 +7570,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44795</v>
+        <v>46092</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7571,7 +7586,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>12.3</v>
+        <v>37.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7629,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7624,14 +7639,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45334</v>
+        <v>46092</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7644,7 +7659,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7687,7 +7702,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7697,14 +7712,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45236</v>
+        <v>46210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7716,13 +7731,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7765,7 +7775,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7775,14 +7785,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45708</v>
+        <v>46210</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7794,13 +7804,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7843,7 +7848,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7857,10 +7862,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46265</v>
+        <v>46210</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7873,7 +7878,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7916,7 +7921,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7926,14 +7931,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45173</v>
+        <v>46265</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,13 +7950,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7994,7 +7994,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46288</v>
+        <v>46147</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>13.6</v>
+        <v>35.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8067,7 +8067,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8081,10 +8081,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46147</v>
+        <v>46288</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>35.7</v>
+        <v>13.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8157,7 +8157,7 @@
         <v>46293</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46287</v>
+        <v>46280</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4.2</v>
+        <v>54.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>54.2</v>
+        <v>4.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 30524-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,45 +1430,159 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.9</v>
+        <v>21.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Mörk blåslav
+Blanksvart spiklav
+Blågrå svartspik
+Gammelgransskål
+Knottrig blåslav
+Kolflarnlav
+Ladlav
+Vedskivlav
+Äggvaxskivling
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 29048-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Knottrig blåslav
@@ -1482,150 +1596,36 @@
 Nordtätskinn</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 30524-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Mörk blåslav
-Blanksvart spiklav
-Blågrå svartspik
-Gammelgransskål
-Knottrig blåslav
-Kolflarnlav
-Ladlav
-Vedskivlav
-Äggvaxskivling
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2371,493 +2371,493 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J17" t="n">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 20780-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 20780-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45776</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lappranunkel
 Stuplav</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 17740-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44896</v>
+        <v>45035</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,23 +2886,28 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>20.1</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2914,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2923,341 +2928,336 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D24" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>100.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
       <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
@@ -3307,7 +3307,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45258</v>
+        <v>46037</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3539,17 +3539,17 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>19.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3572,53 +3572,49 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3632,10 +3628,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45405</v>
+        <v>45258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3648,16 +3644,16 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>19.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -3672,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3681,42 +3677,46 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
         <v>44958</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>45326</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46037</v>
+        <v>45405</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3999,39 +3999,39 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         <v>46265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4160,7 +4160,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44721</v>
+        <v>45361</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.8</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4528,14 +4528,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44687</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44979</v>
+        <v>46024</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4620,13 +4620,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>10.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4669,7 +4664,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4683,10 +4678,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45333</v>
+        <v>46037</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4699,7 +4694,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>31.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4742,7 +4737,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4756,10 +4751,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44795</v>
+        <v>45447</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4772,7 +4767,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>12.3</v>
+        <v>6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4815,7 +4810,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4825,14 +4820,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45162</v>
+        <v>44979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4844,8 +4839,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4898,14 +4898,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45334</v>
+        <v>45217</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4961,7 +4961,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4975,10 +4975,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45361</v>
+        <v>44916</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.4</v>
+        <v>3.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5048,10 +5048,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45331</v>
+        <v>45447</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.9</v>
+        <v>15.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44748</v>
+        <v>45333</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>15.2</v>
+        <v>1.8</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44979</v>
+        <v>45944</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4.6</v>
+        <v>22.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5268,14 +5268,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45293</v>
+        <v>46094</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.8</v>
+        <v>24.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5331,7 +5331,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5341,14 +5341,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45173</v>
+        <v>45426</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5360,13 +5360,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.3</v>
+        <v>62.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5409,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5423,10 +5418,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45426</v>
+        <v>45777</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5439,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>62.1</v>
+        <v>20.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5482,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5496,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45436</v>
+        <v>45776</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5512,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9.699999999999999</v>
+        <v>27.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5555,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5565,14 +5560,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45162</v>
+        <v>46108</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5584,8 +5579,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5628,7 +5628,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5642,10 +5642,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45387</v>
+        <v>46126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5701,7 +5701,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5715,10 +5715,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.2</v>
+        <v>37.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5774,7 +5774,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45162</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5803,8 +5803,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>51.9</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5847,7 +5852,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5857,14 +5862,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45042</v>
+        <v>46092</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5876,13 +5881,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>10.7</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5925,7 +5925,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5935,14 +5935,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45236</v>
+        <v>44721</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5954,13 +5954,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>6.6</v>
+        <v>11.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6003,7 +5998,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6020,7 +6015,7 @@
         <v>44916</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6033,7 +6028,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>13.4</v>
+        <v>7.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6076,7 +6071,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6090,10 +6085,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45447</v>
+        <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6106,7 +6101,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>13.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6149,7 +6144,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6163,10 +6158,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45217</v>
+        <v>45588</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6178,8 +6173,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
         <v>44805</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6305,14 +6305,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45708</v>
+        <v>45596</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6324,13 +6324,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.8</v>
+        <v>17.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6373,7 +6368,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6390,7 +6385,7 @@
         <v>45447</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6403,7 +6398,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>15.6</v>
+        <v>9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6446,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6460,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44916</v>
+        <v>45848</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6476,7 +6471,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6519,7 +6514,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6533,10 +6528,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45546</v>
+        <v>45848</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6549,7 +6544,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>39.8</v>
+        <v>5.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6592,7 +6587,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6606,10 +6601,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45848</v>
+        <v>45546</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6622,7 +6617,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.1</v>
+        <v>39.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6665,7 +6660,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6679,10 +6674,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45848</v>
+        <v>45387</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6695,7 +6690,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6738,7 +6733,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6752,10 +6747,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45588</v>
+        <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,13 +6762,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>3.7</v>
+        <v>11.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6816,7 +6806,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6830,10 +6820,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45944</v>
+        <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6845,13 +6835,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6894,7 +6879,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6904,14 +6889,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45776</v>
+        <v>44687</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6924,7 +6909,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>27.3</v>
+        <v>1.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6967,7 +6952,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6981,10 +6966,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45777</v>
+        <v>44748</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6997,7 +6982,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>20.1</v>
+        <v>15.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7040,7 +7025,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7050,14 +7035,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45596</v>
+        <v>45162</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7070,7 +7055,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>17.4</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7113,7 +7098,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7127,10 +7112,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45447</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7143,7 +7128,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7186,7 +7171,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7200,10 +7185,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46024</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7216,7 +7201,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>10.2</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7259,7 +7244,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7273,10 +7258,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46037</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7289,7 +7274,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>31.3</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7332,7 +7317,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7346,10 +7331,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46094</v>
+        <v>45162</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7362,7 +7347,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>24.5</v>
+        <v>51.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7405,7 +7390,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7419,10 +7404,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46108</v>
+        <v>45293</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7434,13 +7419,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7483,7 +7463,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7497,10 +7477,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46126</v>
+        <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7513,7 +7493,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7556,7 +7536,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7566,14 +7546,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46092</v>
+        <v>45042</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7585,8 +7565,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>37.2</v>
+        <v>10.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7629,7 +7614,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7643,10 +7628,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46092</v>
+        <v>46288</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7659,7 +7644,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>13.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7702,7 +7687,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7716,10 +7701,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46210</v>
+        <v>46147</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7732,7 +7717,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>35.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7775,7 +7760,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7789,10 +7774,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46210</v>
+        <v>44795</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7805,7 +7790,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>12.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7848,7 +7833,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7862,10 +7847,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46210</v>
+        <v>46293</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7878,7 +7863,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6.8</v>
+        <v>9.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7921,7 +7906,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7935,10 +7920,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46265</v>
+        <v>46287</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7951,7 +7936,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7994,7 +7979,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8008,10 +7993,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46147</v>
+        <v>46280</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8024,7 +8009,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>35.7</v>
+        <v>54.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8067,7 +8052,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8077,14 +8062,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46288</v>
+        <v>45334</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8097,7 +8082,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>13.6</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8140,7 +8125,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8150,14 +8135,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46293</v>
+        <v>45236</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8169,8 +8154,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8213,7 +8203,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8223,14 +8213,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46280</v>
+        <v>45708</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,8 +8232,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>54.2</v>
+        <v>0.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8286,7 +8281,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8296,14 +8291,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46287</v>
+        <v>45173</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8315,8 +8310,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30524-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46210</v>
+        <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,19 +1430,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1454,21 +1454,139 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Knottrig blåslav
+Lappmes
+Lavskrika
+Reliktbock
+Sotvaxskivling
+Talltagel
+Vedskivlav
+Vitgrynig nållav
+Nordtätskinn</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 30524-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>22</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>22</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Mörk blåslav
 Blanksvart spiklav
@@ -1482,150 +1600,32 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 29048-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Knottrig blåslav
-Lappmes
-Lavskrika
-Reliktbock
-Sotvaxskivling
-Talltagel
-Vedskivlav
-Vitgrynig nållav
-Nordtätskinn</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1990,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2371,374 +2371,374 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 17740-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2867,14 +2867,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45035</v>
+        <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,28 +2886,23 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>20.1</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2919,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2928,362 +2923,367 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Knottrig blåslav
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3414,10 +3414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3430,17 +3430,17 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3466,50 +3466,46 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3523,10 +3519,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46037</v>
+        <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3539,16 +3535,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3563,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3575,39 +3571,43 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
@@ -3631,7 +3631,7 @@
         <v>45258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3733,14 +3733,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44958</v>
+        <v>45326</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3762,10 +3762,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -3780,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -3789,46 +3789,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45326</v>
+        <v>45405</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3898,42 +3898,42 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3999,46 +3999,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4048,14 +4048,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46265</v>
+        <v>44958</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -4077,10 +4077,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4095,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4108,35 +4108,35 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4459,10 +4459,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45361</v>
+        <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4532,10 +4532,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>17.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4591,7 +4591,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46024</v>
+        <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4664,7 +4664,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46037</v>
+        <v>46024</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>31.3</v>
+        <v>10.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4737,7 +4737,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45447</v>
+        <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6</v>
+        <v>13.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4820,14 +4820,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44979</v>
+        <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4839,13 +4839,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4888,7 +4883,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4902,10 +4897,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45217</v>
+        <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4918,7 +4913,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.3</v>
+        <v>31.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4961,7 +4956,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4975,10 +4970,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44916</v>
+        <v>45217</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4991,7 +4986,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5034,7 +5029,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5048,10 +5043,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45447</v>
+        <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5063,8 +5058,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>15.6</v>
+        <v>22.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5107,7 +5107,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5121,10 +5121,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45333</v>
+        <v>45776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1.8</v>
+        <v>27.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5180,7 +5180,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45944</v>
+        <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5209,13 +5209,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>22.6</v>
+        <v>20.1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5275,7 +5270,7 @@
         <v>46094</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5331,7 +5326,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5341,14 +5336,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45426</v>
+        <v>46108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5360,8 +5355,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>62.1</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5404,7 +5404,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5414,14 +5414,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45777</v>
+        <v>45334</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>20.1</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5477,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45776</v>
+        <v>45361</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>27.3</v>
+        <v>8.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5550,7 +5550,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46108</v>
+        <v>45331</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5579,13 +5579,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5645,7 +5640,7 @@
         <v>46126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5718,7 +5713,7 @@
         <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5774,7 +5769,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5788,10 +5783,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>44748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5803,13 +5798,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>15.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5852,7 +5842,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5866,10 +5856,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46092</v>
+        <v>44979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5881,8 +5871,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5925,7 +5920,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5935,14 +5930,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44721</v>
+        <v>45293</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5955,7 +5950,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5998,7 +5993,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6012,10 +6007,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44916</v>
+        <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6028,7 +6023,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.2</v>
+        <v>51.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6071,7 +6066,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6085,10 +6080,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44916</v>
+        <v>45848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6101,7 +6096,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>13.4</v>
+        <v>5.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6144,7 +6139,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6158,10 +6153,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45588</v>
+        <v>45848</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6173,13 +6168,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6222,7 +6212,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6236,10 +6226,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44805</v>
+        <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6251,8 +6241,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6295,7 +6290,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6309,10 +6304,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45596</v>
+        <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6325,7 +6320,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>17.4</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6368,7 +6363,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6382,10 +6377,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45447</v>
+        <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6397,8 +6392,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6441,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45848</v>
+        <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6470,8 +6470,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6514,7 +6519,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6524,14 +6529,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45848</v>
+        <v>45162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6544,7 +6549,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5.1</v>
+        <v>1.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6587,7 +6592,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6601,10 +6606,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6617,7 +6622,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>39.8</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6660,7 +6665,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6674,10 +6679,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45387</v>
+        <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6690,7 +6695,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8.199999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6733,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,10 +6752,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45162</v>
+        <v>46210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6763,7 +6768,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>11.7</v>
+        <v>6.8</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6823,7 +6828,7 @@
         <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6879,7 +6884,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6889,14 +6894,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44687</v>
+        <v>46265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6909,7 +6914,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6952,7 +6957,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6962,14 +6967,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44748</v>
+        <v>45042</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,8 +6986,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>15.2</v>
+        <v>10.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7025,7 +7035,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,10 +7049,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45162</v>
+        <v>45708</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,8 +7064,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7098,7 +7113,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7112,10 +7127,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7128,7 +7143,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.8</v>
+        <v>35.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7171,7 +7186,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7185,10 +7200,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>45447</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7201,7 +7216,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>15.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7244,7 +7259,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,10 +7273,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>46288</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7274,7 +7289,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>13.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7317,7 +7332,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7331,10 +7346,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45162</v>
+        <v>46293</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7347,7 +7362,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>51.9</v>
+        <v>9.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7390,7 +7405,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7400,14 +7415,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45293</v>
+        <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7420,7 +7435,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>54.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7463,7 +7478,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7477,10 +7492,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46265</v>
+        <v>44916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7493,7 +7508,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7536,7 +7551,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7546,14 +7561,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45042</v>
+        <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7565,13 +7580,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>10.7</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7614,7 +7624,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7628,10 +7638,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46288</v>
+        <v>45546</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7644,7 +7654,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>13.6</v>
+        <v>39.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7687,7 +7697,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7701,10 +7711,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46147</v>
+        <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7717,7 +7727,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>35.7</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7760,7 +7770,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7774,10 +7784,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44795</v>
+        <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7790,7 +7800,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7833,7 +7843,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7843,14 +7853,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46293</v>
+        <v>44687</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7863,7 +7873,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7906,7 +7916,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7920,10 +7930,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46287</v>
+        <v>45333</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7936,7 +7946,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7979,7 +7989,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7993,10 +8003,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46280</v>
+        <v>44795</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8009,7 +8019,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>54.2</v>
+        <v>12.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8052,7 +8062,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8066,10 +8076,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45334</v>
+        <v>45173</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8081,8 +8091,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8125,7 +8140,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8135,14 +8150,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45236</v>
+        <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8154,13 +8169,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>6.6</v>
+        <v>62.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8203,7 +8213,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8213,14 +8223,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45708</v>
+        <v>45387</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8232,13 +8242,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8281,7 +8286,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8291,14 +8296,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45173</v>
+        <v>44916</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8310,13 +8315,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U2" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,6 @@
 Späd brosklav
 Blodticka
 Bårdlav
-Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -782,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +913,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1043,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1174,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1293,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1417,7 +1416,7 @@
         <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1535,7 +1534,7 @@
         <v>46210</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1649,7 +1648,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1761,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1878,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1989,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2099,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2213,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2322,7 +2321,7 @@
         <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2432,7 @@
         <v>45447</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2544,7 +2543,7 @@
         <v>45779</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2655,7 +2654,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2762,7 +2761,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2874,7 +2873,7 @@
         <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2984,7 +2983,7 @@
         <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3090,7 +3089,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3196,7 +3195,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3306,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3416,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3522,7 +3521,7 @@
         <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3631,7 +3630,7 @@
         <v>45258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3740,7 +3739,7 @@
         <v>45326</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3845,7 +3844,7 @@
         <v>45405</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3950,7 +3949,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4055,7 +4054,7 @@
         <v>44958</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4160,7 +4159,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4237,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4315,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4388,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4462,7 +4461,7 @@
         <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4534,7 @@
         <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4608,7 +4607,7 @@
         <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4681,7 +4680,7 @@
         <v>46024</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4754,7 +4753,7 @@
         <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4827,7 +4826,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4900,7 +4899,7 @@
         <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4973,7 +4972,7 @@
         <v>45217</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5046,7 +5045,7 @@
         <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5124,7 +5123,7 @@
         <v>45776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5197,7 +5196,7 @@
         <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5270,7 +5269,7 @@
         <v>46094</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5343,7 +5342,7 @@
         <v>46108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5421,7 +5420,7 @@
         <v>45334</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5494,7 +5493,7 @@
         <v>45361</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5567,7 +5566,7 @@
         <v>45331</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5640,7 +5639,7 @@
         <v>46126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5713,7 +5712,7 @@
         <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5786,7 +5785,7 @@
         <v>44748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5859,7 +5858,7 @@
         <v>44979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5937,7 +5936,7 @@
         <v>45293</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6010,7 +6009,7 @@
         <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6083,7 +6082,7 @@
         <v>45848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6156,7 +6155,7 @@
         <v>45848</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6229,7 +6228,7 @@
         <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6307,7 +6306,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6380,7 +6379,7 @@
         <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6458,7 +6457,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6536,7 +6535,7 @@
         <v>45162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6609,7 +6608,7 @@
         <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6682,7 +6681,7 @@
         <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6755,7 +6754,7 @@
         <v>46210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6828,7 +6827,7 @@
         <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6901,7 +6900,7 @@
         <v>46265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6974,7 +6973,7 @@
         <v>45042</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7052,7 +7051,7 @@
         <v>45708</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7130,7 +7129,7 @@
         <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7203,7 +7202,7 @@
         <v>45447</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7276,7 +7275,7 @@
         <v>46288</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7349,7 +7348,7 @@
         <v>46293</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7422,7 +7421,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7495,7 +7494,7 @@
         <v>44916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7568,7 +7567,7 @@
         <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7641,7 +7640,7 @@
         <v>45546</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7714,7 +7713,7 @@
         <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7787,7 +7786,7 @@
         <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7860,7 +7859,7 @@
         <v>44687</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7933,7 +7932,7 @@
         <v>45333</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8006,7 +8005,7 @@
         <v>44795</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8079,7 +8078,7 @@
         <v>45173</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8157,7 +8156,7 @@
         <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8230,7 +8229,7 @@
         <v>45387</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8303,7 +8302,7 @@
         <v>44916</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8376,7 +8375,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Späd brosklav
 Blodticka
 Bårdlav
+Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -781,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -913,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1044,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1174,7 +1175,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1294,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1416,7 +1417,7 @@
         <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1534,7 +1535,7 @@
         <v>46210</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1648,7 +1649,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1762,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1879,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1989,7 +1990,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2099,7 +2100,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2213,7 +2214,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2321,7 +2322,7 @@
         <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2432,7 +2433,7 @@
         <v>45447</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2543,7 +2544,7 @@
         <v>45779</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2654,7 +2655,7 @@
         <v>45281</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2761,7 +2762,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2873,7 +2874,7 @@
         <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2983,7 +2984,7 @@
         <v>45222</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3089,7 +3090,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3196,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3306,7 +3307,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3416,7 +3417,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3522,7 @@
         <v>45645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3630,7 +3631,7 @@
         <v>45258</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3739,7 +3740,7 @@
         <v>45326</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3844,7 +3845,7 @@
         <v>45405</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3949,7 +3950,7 @@
         <v>46265</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4054,7 +4055,7 @@
         <v>44958</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4160,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4237,7 +4238,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4316,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4389,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4461,7 +4462,7 @@
         <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4534,7 +4535,7 @@
         <v>45596</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4607,7 +4608,7 @@
         <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4680,7 +4681,7 @@
         <v>46024</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4753,7 +4754,7 @@
         <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4826,7 +4827,7 @@
         <v>44805</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4899,7 +4900,7 @@
         <v>46037</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4972,7 +4973,7 @@
         <v>45217</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5045,7 +5046,7 @@
         <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5123,7 +5124,7 @@
         <v>45776</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5196,7 +5197,7 @@
         <v>45777</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5269,7 +5270,7 @@
         <v>46094</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5342,7 +5343,7 @@
         <v>46108</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5420,7 +5421,7 @@
         <v>45334</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5493,7 +5494,7 @@
         <v>45361</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5566,7 +5567,7 @@
         <v>45331</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5639,7 +5640,7 @@
         <v>46126</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5712,7 +5713,7 @@
         <v>46092</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5785,7 +5786,7 @@
         <v>44748</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5858,7 +5859,7 @@
         <v>44979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5936,7 +5937,7 @@
         <v>45293</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6009,7 +6010,7 @@
         <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6082,7 +6083,7 @@
         <v>45848</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6155,7 +6156,7 @@
         <v>45848</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6228,7 +6229,7 @@
         <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6306,7 +6307,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6379,7 +6380,7 @@
         <v>45588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6457,7 +6458,7 @@
         <v>44979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6535,7 +6536,7 @@
         <v>45162</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6608,7 +6609,7 @@
         <v>46210</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6681,7 +6682,7 @@
         <v>46210</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6754,7 +6755,7 @@
         <v>46210</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6827,7 +6828,7 @@
         <v>45436</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6900,7 +6901,7 @@
         <v>46265</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6973,7 +6974,7 @@
         <v>45042</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7051,7 +7052,7 @@
         <v>45708</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7129,7 +7130,7 @@
         <v>46147</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7202,7 +7203,7 @@
         <v>45447</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7275,7 +7276,7 @@
         <v>46288</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7348,7 +7349,7 @@
         <v>46293</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7421,7 +7422,7 @@
         <v>46280</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7494,7 +7495,7 @@
         <v>44916</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7567,7 +7568,7 @@
         <v>46287</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7640,7 +7641,7 @@
         <v>45546</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7713,7 +7714,7 @@
         <v>46092</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7786,7 +7787,7 @@
         <v>44721</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7859,7 +7860,7 @@
         <v>44687</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7932,7 +7933,7 @@
         <v>45333</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8005,7 +8006,7 @@
         <v>44795</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8078,7 +8079,7 @@
         <v>45173</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8156,7 +8157,7 @@
         <v>45426</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8229,7 +8230,7 @@
         <v>45387</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8302,7 +8303,7 @@
         <v>44916</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8375,7 +8376,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U2" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,6 @@
 Späd brosklav
 Blodticka
 Bårdlav
-Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -782,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -795,7 +794,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="J3" t="n">
         <v>5</v>
@@ -914,7 +913,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -927,7 +926,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -960,10 +959,10 @@
         <v>22</v>
       </c>
       <c r="T4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
@@ -1044,7 +1043,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1175,7 +1174,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1294,7 +1293,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1400,7 +1399,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 29048-2026</t>
+          <t>A 30524-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1414,10 +1413,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1430,45 +1429,159 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>16.9</v>
+        <v>21.7</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Mörk blåslav
+Blanksvart spiklav
+Blågrå svartspik
+Gammelgransskål
+Knottrig blåslav
+Kolflarnlav
+Ladlav
+Vedskivlav
+Äggvaxskivling
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 29048-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Knottrig blåslav
@@ -1482,150 +1595,36 @@
 Nordtätskinn</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 30524-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Mörk blåslav
-Blanksvart spiklav
-Blågrå svartspik
-Gammelgransskål
-Knottrig blåslav
-Kolflarnlav
-Ladlav
-Vedskivlav
-Äggvaxskivling
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
     </row>
@@ -1649,7 +1648,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1762,7 +1761,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1879,7 +1878,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1990,7 +1989,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2100,7 +2099,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2214,7 +2213,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2305,7 +2304,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 64829-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2319,10 +2318,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45281</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2335,16 +2334,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>31.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2359,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2371,374 +2370,374 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
     </row>
@@ -2762,7 +2761,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2857,7 +2856,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 53264-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2867,14 +2866,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44896</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2887,13 +2886,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>100.3</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2902,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2911,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2923,230 +2922,230 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 53264-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D23" s="1" t="n">
         <v>45222</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>100.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>2</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
       <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
@@ -3196,7 +3195,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3307,7 +3306,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3417,7 +3416,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3505,7 +3504,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3515,14 +3514,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45645</v>
+        <v>44958</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3535,20 +3534,20 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -3559,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3571,50 +3570,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3628,10 +3623,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45258</v>
+        <v>45326</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,17 +3639,17 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>19.8</v>
+        <v>7.5</v>
       </c>
       <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
@@ -3668,7 +3663,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3677,53 +3672,49 @@
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3737,10 +3728,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45326</v>
+        <v>45405</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3744,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3793,42 +3784,42 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3842,10 +3833,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3858,7 +3849,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3894,46 +3885,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3947,10 +3938,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46265</v>
+        <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3963,16 +3954,16 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.1</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3987,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3999,46 +3990,50 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4048,14 +4043,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44958</v>
+        <v>45258</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4068,10 +4063,10 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>19.8</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -4080,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -4092,51 +4087,55 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
@@ -4160,7 +4159,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4238,7 +4237,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4316,7 +4315,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4389,7 +4388,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4445,7 +4444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4459,10 +4458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45162</v>
+        <v>45361</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4475,7 +4474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4518,7 +4517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4532,10 +4531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45596</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4548,7 +4547,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>17.4</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4591,7 +4590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4608,7 +4607,7 @@
         <v>45447</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4621,7 +4620,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4664,7 +4663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4678,10 +4677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46024</v>
+        <v>44979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4693,8 +4692,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4737,7 +4741,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4754,7 +4758,7 @@
         <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4767,7 +4771,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>13.4</v>
+        <v>3.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4810,7 +4814,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4820,14 +4824,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44805</v>
+        <v>45447</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4840,7 +4844,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>15.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4883,7 +4887,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4897,10 +4901,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46037</v>
+        <v>45333</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4913,7 +4917,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>31.3</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4956,7 +4960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4970,10 +4974,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45217</v>
+        <v>45848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4986,7 +4990,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.3</v>
+        <v>8.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5029,7 +5033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5043,10 +5047,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45944</v>
+        <v>45848</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5058,13 +5062,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>22.6</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5107,7 +5106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5121,10 +5120,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45776</v>
+        <v>45426</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5137,7 +5136,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>27.3</v>
+        <v>62.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5180,7 +5179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5194,10 +5193,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45777</v>
+        <v>44979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5209,8 +5208,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>20.1</v>
+        <v>4.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5253,7 +5257,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5267,10 +5271,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46094</v>
+        <v>45944</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5282,8 +5286,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>24.5</v>
+        <v>22.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5326,7 +5335,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5336,14 +5345,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46108</v>
+        <v>44721</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5355,13 +5364,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>11.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5404,7 +5408,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5414,14 +5418,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45334</v>
+        <v>44916</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5434,7 +5438,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5477,7 +5481,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5491,10 +5495,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45361</v>
+        <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5507,7 +5511,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5550,7 +5554,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5564,10 +5568,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45331</v>
+        <v>45588</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5579,8 +5583,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5623,7 +5632,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5633,14 +5642,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46126</v>
+        <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5653,7 +5662,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.2</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5696,7 +5705,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5710,10 +5719,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46092</v>
+        <v>45777</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5726,7 +5735,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>37.2</v>
+        <v>20.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5769,7 +5778,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5783,10 +5792,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44748</v>
+        <v>45776</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5799,7 +5808,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>15.2</v>
+        <v>27.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5842,7 +5851,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,10 +5865,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44979</v>
+        <v>46094</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5871,13 +5880,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>4.6</v>
+        <v>24.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5920,7 +5924,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5934,10 +5938,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45293</v>
+        <v>46108</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5949,8 +5953,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5993,7 +6002,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6007,10 +6016,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45162</v>
+        <v>46126</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6023,7 +6032,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>51.9</v>
+        <v>5.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6066,7 +6075,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6080,10 +6089,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45848</v>
+        <v>46092</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6096,7 +6105,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.1</v>
+        <v>37.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6139,7 +6148,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6153,10 +6162,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45848</v>
+        <v>45596</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6169,7 +6178,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>8.4</v>
+        <v>17.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6212,7 +6221,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6222,14 +6231,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45236</v>
+        <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6241,13 +6250,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6290,7 +6294,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6304,10 +6308,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45447</v>
+        <v>46024</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6320,7 +6324,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>10.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6363,7 +6367,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6377,10 +6381,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45588</v>
+        <v>46037</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,13 +6396,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>3.7</v>
+        <v>31.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6441,7 +6440,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6455,10 +6454,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44979</v>
+        <v>45546</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6470,13 +6469,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>39.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6519,7 +6513,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6529,14 +6523,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45162</v>
+        <v>45387</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6549,7 +6543,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6592,7 +6586,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6606,10 +6600,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46210</v>
+        <v>45162</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6622,7 +6616,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>11.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6665,7 +6659,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6679,10 +6673,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46210</v>
+        <v>45436</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6695,7 +6689,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6738,7 +6732,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6748,14 +6742,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46210</v>
+        <v>44687</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6768,7 +6762,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.8</v>
+        <v>1.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6811,7 +6805,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6825,10 +6819,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45436</v>
+        <v>44748</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6841,7 +6835,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>9.699999999999999</v>
+        <v>15.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6884,7 +6878,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6894,14 +6888,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46265</v>
+        <v>45162</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6914,7 +6908,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6957,7 +6951,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6967,14 +6961,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45042</v>
+        <v>45162</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,13 +6980,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>10.7</v>
+        <v>51.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7035,7 +7024,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7049,10 +7038,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45708</v>
+        <v>45293</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7062,11 +7051,6 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -7113,7 +7097,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7127,10 +7111,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46147</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7143,7 +7127,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>35.7</v>
+        <v>6.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7186,7 +7170,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7200,10 +7184,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45447</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7216,7 +7200,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>15.6</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7259,7 +7243,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7273,10 +7257,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46288</v>
+        <v>46210</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7289,7 +7273,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>13.6</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7332,7 +7316,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7342,14 +7326,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46293</v>
+        <v>45042</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7361,8 +7345,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7405,7 +7394,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7419,10 +7408,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46280</v>
+        <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7435,7 +7424,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>54.2</v>
+        <v>12.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7478,7 +7467,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7492,10 +7481,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44916</v>
+        <v>46265</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7508,7 +7497,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7551,7 +7540,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7565,10 +7554,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7581,7 +7570,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7624,7 +7613,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7634,14 +7623,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45546</v>
+        <v>45334</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7654,7 +7643,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>39.8</v>
+        <v>2.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7697,7 +7686,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7707,14 +7696,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46092</v>
+        <v>45236</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7726,8 +7715,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7770,7 +7764,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7780,14 +7774,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44721</v>
+        <v>45708</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,8 +7793,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>11.8</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7843,7 +7842,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7853,14 +7852,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44687</v>
+        <v>46147</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7873,7 +7872,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.5</v>
+        <v>35.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7916,7 +7915,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7926,14 +7925,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45333</v>
+        <v>45173</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,8 +7944,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7989,7 +7993,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8003,10 +8007,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44795</v>
+        <v>46293</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8019,7 +8023,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8062,7 +8066,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8072,14 +8076,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45173</v>
+        <v>46287</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8091,13 +8095,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8140,7 +8139,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8154,10 +8153,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45426</v>
+        <v>46280</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8170,7 +8169,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>62.1</v>
+        <v>54.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8213,7 +8212,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8227,10 +8226,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45387</v>
+        <v>46092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8243,7 +8242,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8286,7 +8285,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8300,10 +8299,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44916</v>
+        <v>45217</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8316,7 +8315,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8376,7 +8375,7 @@
         <v>45714</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE90"/>
+  <dimension ref="A1:AE91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>45426</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>45720</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>45035</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 30524-2026</t>
+          <t>A 29048-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46210</v>
+        <v>46199</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>21.7</v>
+        <v>16.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1453,21 +1453,139 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
       </c>
       <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Gammelgransskål
+Knottrig blåslav
+Lappmes
+Lavskrika
+Reliktbock
+Sotvaxskivling
+Talltagel
+Vedskivlav
+Vitgrynig nållav
+Nordtätskinn</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 30524-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>22</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>22</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Mörk blåslav
 Blanksvart spiklav
@@ -1481,150 +1599,32 @@
 Vanlig groda</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 29048-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>10</v>
-      </c>
-      <c r="U9" t="n">
-        <v>10</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gammelgransskål
-Knottrig blåslav
-Lappmes
-Lavskrika
-Reliktbock
-Sotvaxskivling
-Talltagel
-Vedskivlav
-Vitgrynig nållav
-Nordtätskinn</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 64829-2023</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45281</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2334,16 +2334,16 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>31.7</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2370,374 +2370,374 @@
         <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Höstlåsbräken
 Månlåsbräken
 Mattlummer</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 53309-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45229</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Fiskgjuse
-Grönsiska
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
         <v/>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
         <v>45776</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53264-2023</t>
+          <t>A 58860-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2866,14 +2866,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45222</v>
+        <v>44896</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,23 +2886,23 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>100.3</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -2910,10 +2910,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2922,150 +2922,150 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Brun glada
+Salskrake</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Plattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 58860-2022</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Brun glada
-Salskrake</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-      <c r="AE22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
         <v/>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
         <v>45222</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46037</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3514,14 +3514,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44958</v>
+        <v>45326</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>7.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3543,10 +3543,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3570,46 +3570,46 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45326</v>
+        <v>45405</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3679,42 +3679,42 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45405</v>
+        <v>46265</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>6.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3780,46 +3780,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3829,14 +3829,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46265</v>
+        <v>44958</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3858,10 +3858,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3889,35 +3889,35 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
         <v>45645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>45258</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4237,7 +4237,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45361</v>
+        <v>45162</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8.4</v>
+        <v>11.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4517,7 +4517,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45331</v>
+        <v>44916</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4590,7 +4590,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4600,14 +4600,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45447</v>
+        <v>44805</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4663,7 +4663,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44979</v>
+        <v>45217</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4692,13 +4692,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4741,7 +4736,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4755,10 +4750,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44916</v>
+        <v>46037</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4771,7 +4766,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.2</v>
+        <v>31.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4814,7 +4809,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4828,10 +4823,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45447</v>
+        <v>46094</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4844,7 +4839,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>15.6</v>
+        <v>24.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4887,7 +4882,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4901,10 +4896,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45333</v>
+        <v>45944</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4916,8 +4911,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>22.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4960,7 +4960,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4977,7 +4977,7 @@
         <v>45848</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5050,7 +5050,7 @@
         <v>45848</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5116,14 +5116,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45426</v>
+        <v>45334</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>62.1</v>
+        <v>2.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5193,10 +5193,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44979</v>
+        <v>45361</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5208,13 +5208,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>4.6</v>
+        <v>8.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5257,7 +5252,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5267,14 +5262,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45944</v>
+        <v>46108</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5288,11 +5283,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>22.6</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5335,7 +5330,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5349,10 +5344,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44721</v>
+        <v>46126</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5365,7 +5360,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>11.8</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5408,7 +5403,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5422,10 +5417,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44916</v>
+        <v>46092</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5438,7 +5433,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>7.2</v>
+        <v>37.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5481,7 +5476,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44916</v>
+        <v>45331</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5511,7 +5506,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5554,7 +5549,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5568,10 +5563,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45588</v>
+        <v>45776</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5583,13 +5578,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>3.7</v>
+        <v>27.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5632,7 +5622,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5642,14 +5632,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44805</v>
+        <v>45777</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5662,7 +5652,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>20.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5705,7 +5695,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5719,10 +5709,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45777</v>
+        <v>44748</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5735,7 +5725,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>20.1</v>
+        <v>15.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5778,7 +5768,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5792,10 +5782,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45776</v>
+        <v>44979</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5807,8 +5797,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>27.3</v>
+        <v>4.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5851,7 +5846,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5861,14 +5856,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46094</v>
+        <v>45293</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5881,7 +5876,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>24.5</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5924,7 +5919,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5934,14 +5929,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46108</v>
+        <v>45596</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5953,13 +5948,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>17.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6002,7 +5992,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6016,10 +6006,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46126</v>
+        <v>45447</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6032,7 +6022,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6075,7 +6065,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6089,10 +6079,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46092</v>
+        <v>46024</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6105,7 +6095,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>37.2</v>
+        <v>10.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6148,7 +6138,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6162,10 +6152,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45596</v>
+        <v>45162</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6178,7 +6168,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>17.4</v>
+        <v>51.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6221,7 +6211,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6231,14 +6221,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45447</v>
+        <v>45236</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6250,8 +6240,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6294,7 +6289,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6308,10 +6303,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46024</v>
+        <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6324,7 +6319,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>10.2</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6367,7 +6362,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6381,10 +6376,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46037</v>
+        <v>46210</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6397,7 +6392,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>31.3</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6440,7 +6435,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6454,10 +6449,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45546</v>
+        <v>46210</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6470,7 +6465,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>39.8</v>
+        <v>2.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6513,7 +6508,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6527,10 +6522,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45387</v>
+        <v>46210</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6543,7 +6538,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6586,7 +6581,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6600,10 +6595,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45162</v>
+        <v>45588</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6615,8 +6610,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>11.7</v>
+        <v>3.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45436</v>
+        <v>44979</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6688,8 +6688,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.699999999999999</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6732,7 +6737,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6746,10 +6751,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44687</v>
+        <v>45162</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6762,7 +6767,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6805,7 +6810,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6819,10 +6824,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44748</v>
+        <v>46265</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6835,7 +6840,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>15.2</v>
+        <v>2.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6878,7 +6883,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6888,14 +6893,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45162</v>
+        <v>45436</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6908,7 +6913,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6951,7 +6956,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6965,10 +6970,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45162</v>
+        <v>46147</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6981,7 +6986,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>51.9</v>
+        <v>35.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7024,7 +7029,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7034,14 +7039,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45293</v>
+        <v>46288</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7054,7 +7059,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>13.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7097,7 +7102,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7111,10 +7116,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46210</v>
+        <v>46293</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7127,7 +7132,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.8</v>
+        <v>9.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7170,7 +7175,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7184,10 +7189,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46210</v>
+        <v>46280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7200,7 +7205,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>54.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7243,7 +7248,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7253,14 +7258,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46210</v>
+        <v>45042</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7272,8 +7277,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>10.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7316,7 +7326,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7326,14 +7336,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45042</v>
+        <v>46287</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7345,13 +7355,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>10.7</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7394,7 +7399,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7404,14 +7409,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44795</v>
+        <v>45708</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7423,8 +7428,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>12.3</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7467,7 +7477,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7481,10 +7491,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46265</v>
+        <v>45447</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7497,7 +7507,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>15.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7540,7 +7550,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7554,10 +7564,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46288</v>
+        <v>46092</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7570,7 +7580,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>13.6</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7613,7 +7623,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7623,14 +7633,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45334</v>
+        <v>44916</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7643,7 +7653,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7686,7 +7696,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 41451-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7696,14 +7706,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45236</v>
+        <v>46301</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7715,13 +7725,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>6.6</v>
+        <v>28.1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7764,7 +7769,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7774,14 +7779,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45708</v>
+        <v>45546</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7793,13 +7798,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>39.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7842,7 +7842,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7856,10 +7856,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46147</v>
+        <v>44721</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>35.7</v>
+        <v>11.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7915,7 +7915,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45173</v>
+        <v>44687</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7944,13 +7944,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7993,7 +7988,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8007,10 +8002,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46293</v>
+        <v>45333</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8023,7 +8018,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>9.5</v>
+        <v>1.8</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8066,7 +8061,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8080,10 +8075,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46287</v>
+        <v>44795</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8096,7 +8091,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.2</v>
+        <v>12.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8139,7 +8134,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8149,14 +8144,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46280</v>
+        <v>45173</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8168,8 +8163,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>54.2</v>
+        <v>1.3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8212,7 +8212,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8226,10 +8226,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46092</v>
+        <v>45426</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>62.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8299,10 +8299,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45217</v>
+        <v>45387</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8355,78 +8355,151 @@
       </c>
       <c r="V89" s="2" t="inlineStr"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
+          <t>A 62439-2022</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>44916</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>S 637-2025</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D90" s="1" t="n">
+      <c r="D91" s="1" t="n">
         <v>45714</v>
       </c>
-      <c r="E90" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
+      <c r="E91" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
         <v>49.3</v>
       </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="2" t="inlineStr"/>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U2" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,6 +696,7 @@
 Späd brosklav
 Blodticka
 Bårdlav
+Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -781,7 +782,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -913,7 +914,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1026,7 +1027,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 18726-2024</t>
+          <t>A 30524-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1040,10 +1041,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45426</v>
+        <v>46210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1055,51 +1056,175 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>21.7</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>16</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="n">
+        <v>37</v>
+      </c>
+      <c r="U5" t="n">
+        <v>37</v>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Mörk blåslav
+Blanksvart spiklav
+Blågrå svartspik
+Dropptaggsvamp
+Gammelgransskål
+Grantaggsvamp
+Hornvaxskinn
+Knottrig blåslav
+Kolflarnlav
+Ladlav
+Mörk kolflarnlav
+Talltagel
+Ullticka
+Vedflamlav
+Vedskivlav
+Äggvaxskivling
+Gullgröppa
+Vedticka
+Vågbandad barkbock
+Vanlig groda</t>
+        </is>
+      </c>
+      <c r="W5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="X5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="Y5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AA5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AB5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AC5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+      <c r="AD5">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A 18726-2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45426</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>11</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>18</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>7</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>18</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>88</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>17</v>
       </c>
-      <c r="V5" s="2" t="inlineStr">
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Goliatmusseron
@@ -1121,111 +1246,111 @@
 Vitplätt</t>
         </is>
       </c>
-      <c r="W5">
+      <c r="W6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 18726-2024 artfynd.xlsx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="X5">
+      <c r="X6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 18726-2024 karta.png", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="Y5">
+      <c r="Y6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 18726-2024 georefererad karta.tif", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AA5">
+      <c r="AA6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 18726-2024 FSC-klagomål.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AB5">
+      <c r="AB6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 18726-2024 FSC-klagomål mail.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AC5">
+      <c r="AC6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 18726-2024 tillsynsbegäran.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AD5">
+      <c r="AD6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 18726-2024 tillsynsbegäran mail.docx", "A 18726-2024")</f>
         <v/>
       </c>
-      <c r="AE5">
+      <c r="AE6">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 18726-2024 prioriterade fågelarter.docx", "A 18726-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
         <is>
           <t>S 698-2025</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Traktorväg</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D7" s="1" t="n">
         <v>45720</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="E7" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>62.2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>9</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>2</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S7" t="n">
         <v>11</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>41</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>41</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Gräddporing
@@ -1240,116 +1365,116 @@
 Utter</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/S 698-2025 artfynd.xlsx", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/S 698-2025 karta.png", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/S 698-2025 georefererad karta.tif", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/S 698-2025 FSC-klagomål.docx", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/S 698-2025 FSC-klagomål mail.docx", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/S 698-2025 tillsynsbegäran.docx", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/S 698-2025 tillsynsbegäran mail.docx", "S 698-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/S 698-2025 prioriterade fågelarter.docx", "S 698-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 17705-2023</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45035</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>58.9</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>10</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>12</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Fläckporing
 Gräddporing
@@ -1363,111 +1488,111 @@
 Svartvit flugsnappare</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17705-2023 artfynd.xlsx", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17705-2023 karta.png", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17705-2023 georefererad karta.tif", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17705-2023 FSC-klagomål.docx", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17705-2023 FSC-klagomål mail.docx", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17705-2023 tillsynsbegäran.docx", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17705-2023 tillsynsbegäran mail.docx", "A 17705-2023")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 17705-2023 prioriterade fågelarter.docx", "A 17705-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>A 29048-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D9" s="1" t="n">
         <v>46199</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
+      <c r="E9" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>16.9</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>9</v>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>10</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
         <v>10</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>10</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Gammelgransskål
 Knottrig blåslav
@@ -1481,150 +1606,36 @@
 Nordtätskinn</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 29048-2026 artfynd.xlsx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 29048-2026 karta.png", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 29048-2026 georefererad karta.tif", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 29048-2026 FSC-klagomål.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 29048-2026 FSC-klagomål mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 29048-2026 tillsynsbegäran.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 29048-2026 tillsynsbegäran mail.docx", "A 29048-2026")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 29048-2026 prioriterade fågelarter.docx", "A 29048-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 30524-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="n">
-        <v>22</v>
-      </c>
-      <c r="U9" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Mörk blåslav
-Blanksvart spiklav
-Blågrå svartspik
-Gammelgransskål
-Knottrig blåslav
-Kolflarnlav
-Ladlav
-Vedskivlav
-Äggvaxskivling
-Vanlig groda</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 30524-2026 artfynd.xlsx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 30524-2026 karta.png", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 30524-2026 georefererad karta.tif", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 30524-2026 FSC-klagomål.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 30524-2026 FSC-klagomål mail.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 30524-2026 tillsynsbegäran.docx", "A 30524-2026")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 30524-2026 tillsynsbegäran mail.docx", "A 30524-2026")</f>
         <v/>
       </c>
     </row>
@@ -1648,7 +1659,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1761,7 +1772,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1878,7 +1889,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1989,7 +2000,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2099,7 +2110,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2213,7 +2224,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2304,7 +2315,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53309-2023</t>
+          <t>A 20780-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2314,14 +2325,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45776</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2333,20 +2344,25 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2358,505 +2374,500 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Lappranunkel
+Stuplav</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>3</v>
       </c>
-      <c r="U16" t="n">
+      <c r="T17" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 53309-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45229</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Fiskgjuse
 Grönsiska
 Havsörn</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 22495-2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>45447</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Tajgafältmätare
-Blåhake
-Lavskrika</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A 21183-2025</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45779</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>Lappmes
-Venhavre
-Kärrtrumpetmossa</t>
-        </is>
-      </c>
-      <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 64829-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Avverkning för annat ändamål</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45281</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Höstlåsbräken
-Månlåsbräken
-Mattlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 20780-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45776</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Lappranunkel
-Stuplav</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58860-2022</t>
+          <t>A 53264-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2866,14 +2877,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44896</v>
+        <v>45222</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2886,13 +2897,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>100.3</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2901,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2910,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>2</v>
@@ -2922,367 +2933,367 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 53264-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45222</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="J22" t="n">
         <v>2</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Plattlummer
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 17740-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45035</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav
+Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 58860-2022</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Brun glada
 Salskrake</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 58860-2022 artfynd.xlsx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 58860-2022 karta.png", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 58860-2022 georefererad karta.tif", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 58860-2022 FSC-klagomål.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 58860-2022 FSC-klagomål mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 58860-2022 tillsynsbegäran.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 58860-2022 tillsynsbegäran mail.docx", "A 58860-2022")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 58860-2022 prioriterade fågelarter.docx", "A 58860-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 53264-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45222</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>100.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Plattlummer
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53264-2023 artfynd.xlsx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53264-2023 karta.png", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53264-2023 georefererad karta.tif", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53264-2023 FSC-klagomål.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53264-2023 FSC-klagomål mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53264-2023 tillsynsbegäran.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53264-2023 tillsynsbegäran mail.docx", "A 53264-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 17740-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45035</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>NORRBOTTENS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>KIRUNA</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Knottrig blåslav
-Svartvit flugsnappare</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 17740-2023 artfynd.xlsx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 17740-2023 karta.png", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 17740-2023 georefererad karta.tif", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 17740-2023 FSC-klagomål.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 17740-2023 FSC-klagomål mail.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 17740-2023 tillsynsbegäran.docx", "A 17740-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 17740-2023 tillsynsbegäran mail.docx", "A 17740-2023")</f>
         <v/>
       </c>
     </row>
@@ -3306,7 +3317,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3399,7 +3410,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 2660-2026</t>
+          <t>A 61066-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3413,10 +3424,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46037</v>
+        <v>45645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3429,16 +3440,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3453,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3465,46 +3476,50 @@
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4367-2024</t>
+          <t>A 60064-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3518,10 +3533,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45326</v>
+        <v>45258</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,16 +3549,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>7.5</v>
+        <v>19.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3558,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3567,49 +3582,53 @@
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16024-2024</t>
+          <t>A 5842-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3619,14 +3638,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45405</v>
+        <v>44958</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3639,7 +3658,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3648,10 +3667,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -3666,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3675,46 +3694,46 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällsotlav</t>
         </is>
       </c>
       <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35757-2026</t>
+          <t>A 4367-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3728,10 +3747,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46265</v>
+        <v>45326</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3744,7 +3763,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3780,46 +3799,46 @@
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 4367-2024 artfynd.xlsx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 4367-2024 karta.png", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 4367-2024 georefererad karta.tif", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 4367-2024 FSC-klagomål.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 4367-2024 FSC-klagomål mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 4367-2024 tillsynsbegäran.docx", "A 4367-2024")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 4367-2024 tillsynsbegäran mail.docx", "A 4367-2024")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 5842-2023</t>
+          <t>A 16024-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3829,14 +3848,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44958</v>
+        <v>45405</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3849,7 +3868,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3858,10 +3877,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -3876,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -3885,46 +3904,46 @@
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>Fjällsotlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 5842-2023 artfynd.xlsx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 16024-2024 artfynd.xlsx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 5842-2023 karta.png", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 16024-2024 karta.png", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 5842-2023 georefererad karta.tif", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 16024-2024 georefererad karta.tif", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 5842-2023 FSC-klagomål.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 16024-2024 FSC-klagomål.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 5842-2023 FSC-klagomål mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 16024-2024 FSC-klagomål mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 5842-2023 tillsynsbegäran.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 16024-2024 tillsynsbegäran.docx", "A 16024-2024")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 5842-2023 tillsynsbegäran mail.docx", "A 5842-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 16024-2024 tillsynsbegäran mail.docx", "A 16024-2024")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 61066-2024</t>
+          <t>A 2660-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3938,10 +3957,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45645</v>
+        <v>46037</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3954,17 +3973,17 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -3978,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -3990,50 +4009,46 @@
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 61066-2024 artfynd.xlsx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 2660-2026 artfynd.xlsx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 61066-2024 karta.png", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 2660-2026 karta.png", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 61066-2024 georefererad karta.tif", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 2660-2026 georefererad karta.tif", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 61066-2024 FSC-klagomål.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 2660-2026 FSC-klagomål.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 61066-2024 FSC-klagomål mail.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 2660-2026 FSC-klagomål mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 61066-2024 tillsynsbegäran.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 2660-2026 tillsynsbegäran.docx", "A 2660-2026")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 61066-2024 tillsynsbegäran mail.docx", "A 61066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 61066-2024 prioriterade fågelarter.docx", "A 61066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 2660-2026 tillsynsbegäran mail.docx", "A 2660-2026")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 60064-2023</t>
+          <t>A 35757-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4047,10 +4062,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45258</v>
+        <v>46265</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4063,17 +4078,17 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>19.8</v>
+        <v>6.1</v>
       </c>
       <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
@@ -4087,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4096,46 +4111,42 @@
         <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 60064-2023 artfynd.xlsx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 35757-2026 artfynd.xlsx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 60064-2023 karta.png", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 35757-2026 karta.png", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 60064-2023 georefererad karta.tif", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 35757-2026 georefererad karta.tif", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 60064-2023 FSC-klagomål.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 35757-2026 FSC-klagomål.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 60064-2023 FSC-klagomål mail.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 35757-2026 FSC-klagomål mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 60064-2023 tillsynsbegäran.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 35757-2026 tillsynsbegäran.docx", "A 35757-2026")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 60064-2023 tillsynsbegäran mail.docx", "A 60064-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 60064-2023 prioriterade fågelarter.docx", "A 60064-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 35757-2026 tillsynsbegäran mail.docx", "A 35757-2026")</f>
         <v/>
       </c>
     </row>
@@ -4159,7 +4170,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4237,7 +4248,7 @@
         <v>44875</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4315,7 +4326,7 @@
         <v>44623</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4388,7 +4399,7 @@
         <v>44623</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4444,7 +4455,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39247-2023</t>
+          <t>A 9605-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4458,10 +4469,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45162</v>
+        <v>45361</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4474,7 +4485,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>11.7</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -4517,7 +4528,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62460-2022</t>
+          <t>A 5411-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4531,10 +4542,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44916</v>
+        <v>45331</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4547,7 +4558,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>13.4</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4590,7 +4601,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36939-2022</t>
+          <t>A 50590-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4600,14 +4611,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44805</v>
+        <v>45217</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4620,7 +4631,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4663,7 +4674,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50590-2023</t>
+          <t>A 22494-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4677,10 +4688,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45217</v>
+        <v>45447</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4693,7 +4704,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4736,7 +4747,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 2664-2026</t>
+          <t>A 38577-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4750,10 +4761,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46037</v>
+        <v>45546</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4766,7 +4777,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>31.3</v>
+        <v>39.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4809,7 +4820,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13405-2026</t>
+          <t>A 9069-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4823,10 +4834,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46094</v>
+        <v>44979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4838,8 +4849,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>24.5</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4882,7 +4898,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 50338-2025</t>
+          <t>A 13526-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4896,10 +4912,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45944</v>
+        <v>45387</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4911,13 +4927,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>22.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4960,7 +4971,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 34663-2025</t>
+          <t>A 39247-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4974,10 +4985,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45848</v>
+        <v>45162</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4990,7 +5001,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>11.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5033,7 +5044,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 34664-2025</t>
+          <t>A 50338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5047,10 +5058,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45848</v>
+        <v>45944</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5062,8 +5073,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>8.4</v>
+        <v>22.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5106,7 +5122,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 5533-2024</t>
+          <t>A 62439-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5116,14 +5132,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45334</v>
+        <v>44916</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5136,7 +5152,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5179,7 +5195,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 9605-2024</t>
+          <t>A 22504-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5193,10 +5209,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45361</v>
+        <v>45447</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5209,7 +5225,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>8.4</v>
+        <v>15.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5252,7 +5268,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16197-2026</t>
+          <t>A 20744-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5262,14 +5278,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46108</v>
+        <v>45436</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5281,13 +5297,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5330,7 +5341,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 18388-2026</t>
+          <t>A 5476-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5344,10 +5355,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46126</v>
+        <v>45333</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5360,7 +5371,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>1.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5403,7 +5414,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12937-2026</t>
+          <t>A 34664-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5417,10 +5428,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46092</v>
+        <v>45848</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5433,7 +5444,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>37.2</v>
+        <v>8.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5476,7 +5487,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 5411-2024</t>
+          <t>A 34663-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5490,10 +5501,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45331</v>
+        <v>45848</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5506,7 +5517,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5549,7 +5560,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20893-2025</t>
+          <t>A 21184-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5563,10 +5574,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45776</v>
+        <v>45777</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5579,7 +5590,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>27.3</v>
+        <v>20.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5622,7 +5633,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 21184-2025</t>
+          <t>A 20893-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5636,10 +5647,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45777</v>
+        <v>45776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5652,7 +5663,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>20.1</v>
+        <v>27.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5695,7 +5706,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 28707-2022</t>
+          <t>A 18721-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5709,10 +5720,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44748</v>
+        <v>45426</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5725,7 +5736,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>15.2</v>
+        <v>62.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5768,7 +5779,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 9068-2023</t>
+          <t>A 18738-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5778,14 +5789,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44979</v>
+        <v>44687</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5797,13 +5808,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>4.6</v>
+        <v>1.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5846,7 +5852,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 93-2024</t>
+          <t>A 9068-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5856,14 +5862,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45293</v>
+        <v>44979</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5875,8 +5881,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5919,7 +5930,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 49704-2024</t>
+          <t>A 28707-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5933,10 +5944,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45596</v>
+        <v>44748</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5949,7 +5960,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>17.4</v>
+        <v>15.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5992,7 +6003,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 22491-2024</t>
+          <t>A 39006-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6002,14 +6013,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45447</v>
+        <v>45162</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6022,7 +6033,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6065,7 +6076,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 148-2026</t>
+          <t>A 23469-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6079,10 +6090,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46024</v>
+        <v>44721</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6095,7 +6106,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>10.2</v>
+        <v>11.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6138,7 +6149,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39271-2023</t>
+          <t>A 62452-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6152,10 +6163,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45162</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6168,7 +6179,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>51.9</v>
+        <v>7.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6211,7 +6222,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56168-2023</t>
+          <t>A 62460-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6221,14 +6232,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45236</v>
+        <v>44916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6240,13 +6251,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>6.6</v>
+        <v>13.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6289,7 +6295,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 22494-2024</t>
+          <t>A 39271-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6303,10 +6309,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45447</v>
+        <v>45162</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6319,7 +6325,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>51.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6362,7 +6368,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 30594-2026</t>
+          <t>A 22491-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6376,10 +6382,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46210</v>
+        <v>45447</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6392,7 +6398,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6435,7 +6441,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 30591-2026</t>
+          <t>A 47730-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6449,10 +6455,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46210</v>
+        <v>45588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6464,8 +6470,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.1</v>
+        <v>3.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6508,7 +6519,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 30562-2026</t>
+          <t>A 36939-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6518,14 +6529,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46210</v>
+        <v>44805</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6538,7 +6549,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6581,7 +6592,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 47730-2024</t>
+          <t>A 148-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6595,10 +6606,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45588</v>
+        <v>46024</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6610,13 +6621,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>3.7</v>
+        <v>10.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6659,7 +6665,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 9069-2023</t>
+          <t>A 93-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6669,14 +6675,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44979</v>
+        <v>45293</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6688,13 +6694,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6737,7 +6738,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 39006-2023</t>
+          <t>A 2664-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6747,14 +6748,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45162</v>
+        <v>46037</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6767,7 +6768,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>31.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6810,7 +6811,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35765-2026</t>
+          <t>A 18737-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6820,14 +6821,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46265</v>
+        <v>45042</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6839,8 +6840,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>2.7</v>
+        <v>10.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6883,7 +6889,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20744-2024</t>
+          <t>A 13405-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6897,10 +6903,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45436</v>
+        <v>46094</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6913,7 +6919,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.699999999999999</v>
+        <v>24.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6956,7 +6962,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 21268-2026</t>
+          <t>A 30562-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6970,10 +6976,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46147</v>
+        <v>46210</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6986,7 +6992,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>35.7</v>
+        <v>6.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7029,7 +7035,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 39321-2026</t>
+          <t>A 16197-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7039,14 +7045,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46288</v>
+        <v>46108</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7058,8 +7064,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>13.6</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7102,7 +7113,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 40136-2026</t>
+          <t>A 30594-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7116,10 +7127,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46293</v>
+        <v>46210</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7132,7 +7143,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7175,7 +7186,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37993-2026</t>
+          <t>A 30591-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7189,10 +7200,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46280</v>
+        <v>46210</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7205,7 +7216,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>54.2</v>
+        <v>2.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7248,7 +7259,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 18737-2023</t>
+          <t>A 34693-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7258,14 +7269,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45042</v>
+        <v>44795</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7277,13 +7288,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7326,7 +7332,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 39064-2026</t>
+          <t>A 18388-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7340,10 +7346,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46287</v>
+        <v>46126</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7356,7 +7362,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7399,7 +7405,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 8350-2025</t>
+          <t>A 12937-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7409,14 +7415,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45708</v>
+        <v>46092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7428,13 +7434,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.8</v>
+        <v>37.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7477,7 +7478,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 22504-2024</t>
+          <t>A 5533-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7487,14 +7488,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45447</v>
+        <v>45334</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7507,7 +7508,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>15.6</v>
+        <v>2.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7550,7 +7551,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12969-2026</t>
+          <t>A 56168-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7560,14 +7561,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46092</v>
+        <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7579,8 +7580,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7623,7 +7629,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 62452-2022</t>
+          <t>A 8350-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7633,14 +7639,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44916</v>
+        <v>45708</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7652,8 +7658,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7696,7 +7707,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 41451-2026</t>
+          <t>A 41127-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7706,14 +7717,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46301</v>
+        <v>45173</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7725,8 +7736,13 @@
           <t>KIRUNA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>28.1</v>
+        <v>1.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7769,7 +7785,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 38577-2024</t>
+          <t>A 35765-2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7783,10 +7799,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45546</v>
+        <v>46265</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7799,7 +7815,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>39.8</v>
+        <v>2.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -7842,7 +7858,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 23469-2022</t>
+          <t>A 39321-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7856,10 +7872,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44721</v>
+        <v>46288</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7872,7 +7888,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>11.8</v>
+        <v>13.6</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7915,7 +7931,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 18738-2022</t>
+          <t>A 21268-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7925,14 +7941,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44687</v>
+        <v>46147</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7945,7 +7961,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.5</v>
+        <v>35.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7988,7 +8004,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5476-2024</t>
+          <t>A 40136-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8002,10 +8018,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45333</v>
+        <v>46293</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8018,7 +8034,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8061,7 +8077,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 34693-2022</t>
+          <t>A 39064-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8075,10 +8091,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44795</v>
+        <v>46287</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8091,7 +8107,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>12.3</v>
+        <v>4.2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8134,7 +8150,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41127-2023</t>
+          <t>A 37993-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8144,14 +8160,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45173</v>
+        <v>46280</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8163,13 +8179,8 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>1.3</v>
+        <v>54.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8212,7 +8223,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 18721-2024</t>
+          <t>A 12969-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8226,10 +8237,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45426</v>
+        <v>46092</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8242,7 +8253,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>62.1</v>
+        <v>5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8285,7 +8296,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13526-2024</t>
+          <t>A 41451-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8299,10 +8310,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45387</v>
+        <v>46301</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8315,7 +8326,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>8.199999999999999</v>
+        <v>28.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8358,7 +8369,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 62439-2022</t>
+          <t>A 49704-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8372,10 +8383,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44916</v>
+        <v>45596</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8388,7 +8399,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3.2</v>
+        <v>17.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8448,7 +8459,7 @@
         <v>45714</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>

--- a/Översikt KIRUNA.xlsx
+++ b/Översikt KIRUNA.xlsx
@@ -601,7 +601,7 @@
         <v>44624</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
         <v>29</v>
@@ -644,13 +644,13 @@
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U2" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -696,7 +696,6 @@
 Späd brosklav
 Blodticka
 Bårdlav
-Diskvaxskivling
 Finbräken
 Gräsull
 Grönkulla
@@ -782,7 +781,7 @@
         <v>46210</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -914,7 +913,7 @@
         <v>46244</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1044,7 +1043,7 @@
         <v>46210</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1168,7 +1167,7 @@
         <v>45426</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1299,7 +1298,7 @@
         <v>45720</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1418,7 +1417,7 @@
         <v>45035</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1541,7 +1540,7 @@
         <v>46199</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1659,7 +1658,7 @@
         <v>46000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1772,7 +1771,7 @@
         <v>46202</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1889,7 +1888,7 @@
         <v>46202</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2000,7 +1999,7 @@
         <v>46202</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2110,7 +2109,7 @@
         <v>45775</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2224,7 +2223,7 @@
         <v>46170</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2314,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 20780-2025</t>
+          <t>A 53309-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2325,14 +2324,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45776</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2344,25 +2343,20 @@
           <t>KIRUNA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2374,500 +2368,505 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
       </c>
       <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Fiskgjuse
+Grönsiska
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 53309-2023 artfynd.xlsx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 53309-2023 karta.png", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 53309-2023 georefererad karta.tif", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 53309-2023 FSC-klagomål.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 53309-2023 FSC-klagomål mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 53309-2023 tillsynsbegäran.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 53309-2023 tillsynsbegäran mail.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 53309-2023 prioriterade fågelarter.docx", "A 53309-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A 22495-2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45447</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Tajgafältmätare
+Blåhake
+Lavskrika</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 22495-2024 artfynd.xlsx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 22495-2024 karta.png", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 22495-2024 georefererad karta.tif", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 22495-2024 FSC-klagomål.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 22495-2024 FSC-klagomål mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 22495-2024 tillsynsbegäran.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 22495-2024 tillsynsbegäran mail.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 22495-2024 prioriterade fågelarter.docx", "A 22495-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 21183-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45779</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Lappmes
+Venhavre
+Kärrtrumpetmossa</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 21183-2025 artfynd.xlsx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 21183-2025 karta.png", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 21183-2025 georefererad karta.tif", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 21183-2025 FSC-klagomål.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 21183-2025 FSC-klagomål mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 21183-2025 tillsynsbegäran.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 21183-2025 tillsynsbegäran mail.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/fåglar/A 21183-2025 prioriterade fågelarter.docx", "A 21183-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 64829-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Avverkning för annat ändamål</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45281</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Höstlåsbräken
+Månlåsbräken
+Mattlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 64829-2023 artfynd.xlsx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 64829-2023 karta.png", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 64829-2023 georefererad karta.tif", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 64829-2023 FSC-klagomål.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 64829-2023 FSC-klagomål mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 64829-2023 tillsynsbegäran.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 64829-2023 tillsynsbegäran mail.docx", "A 64829-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 20780-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45776</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>NORRBOTTENS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>KIRUNA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Lappranunkel
 Stuplav</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/artfynd/A 20780-2025 artfynd.xlsx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor/A 20780-2025 karta.png", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/kartor_geotiff/A 20780-2025 georefererad karta.tif", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomål/A 20780-2025 FSC-klagomål.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/klagomålsmail/A 20780-2025 FSC-klagomål mail.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsyn/A 20780-2025 tillsynsbegäran.docx", "A 20780-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2584/tillsynsmail/A 20780-2025 tillsynsbegäran mail.docx", "A 20780-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        